--- a/docs/traceability-matrix.xlsx
+++ b/docs/traceability-matrix.xlsx
@@ -1,23 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MEUX LAB\MEUX LAB DEV\meux-lab\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F128BA94-259B-4499-8A70-8CC51E6EC430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Matriz de Trazabilidad" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Resumen por Épica" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Cobertura RNF" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Matriz de Trazabilidad" sheetId="1" r:id="rId1"/>
+    <sheet name="Resumen por Épica" sheetId="2" r:id="rId2"/>
+    <sheet name="Cobertura RNF" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Cobertura RNF'!$A$1:$F$30</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Matriz de Trazabilidad'!$A$1:$M$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cobertura RNF'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matriz de Trazabilidad'!$A$1:$M$200</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,1876 +42,1873 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2779" uniqueCount="620">
-  <si>
-    <t xml:space="preserve">ID RF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado Épica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actor(es)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Origen (Pantalla)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descripción del RF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF Relacionados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prioridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dificultad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoSCoW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 1 - Núcleo y Seguridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investigador; Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONBOARDING SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar a la siguiente pantalla de información en la Pantalla de Bienvenida (Onboarding) deslizando la pantalla hacia la izquierda o haciendo clic en icono de flecha, permitiendo la visualización secuencial de las características clave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0011, RNF0012, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could have</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANDING PAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Registro haciendo clic en el botón de "Registrarse" ubicado en el Header de la Landing Page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0004, RNF0011, RNF0012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must have</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Inicio de sesión haciendo clic en el botón de "Iniciar Sesión" ubicado en el Header de la Landing Page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Inicio de sesión haciendo clic en el botón “Empieza Ya” ubicado al final de la Landing Page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Should have</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Registro haciendo clic en el enlace hipertexto “¿No tienes cuenta? Regístrate” para completar el formulario de registro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede hacer clic en el logo “MEUX Lab” para regresar a la Landing Page desde la Pantalla de Registro/Inicio de Sesión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIGN UP SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Inicio de sesión haciendo clic en el enlace hipertexto “¿Ya tienes cuenta? Inicia sesión” para introducir sus credenciales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario completa un formulario en la Pantalla de Registro llenando los campos correspondientes y pulsa el botón de “Registrar” para crear una cuenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0006, RNF0009, RNF0011, RNF0029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Términos y Condiciones haciendo clic en el enlace de hipertexto ubicado al final del formulario de la Pantalla de Registro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0011, RNF0029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Políticas de Privacidad haciendo clic en el enlace de hipertexto ubicado al final del formulario de la Pantalla de Registro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe marcar la casilla de aceptación para los Términos y Condiciones y la Política de Privacidad en el formulario de la Pantalla de Registro para crear una cuenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0009, RNF0011, RNF0029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOGIN SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario introduce sus credenciales en la Pantalla de Inicio de Sesión llenando los campos correspondientes y pulsa el botón de “Iniciar Sesión” para ingresar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0006, RNF0007, RNF0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede pulsar el botón “Inicio de sesión con Google” para ingresar mediante cuentas de Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0006, RNF0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede alternar la visibilidad de la contraseña haciendo clic en el ícono de Ojo dentro del campo de entrada de contraseña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0013, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el proceso de recuperación de contraseña haciendo clic en el enlace hipertexto “¿Olvidaste la contraseña?”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0004, RNF0011, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASSWORD RECOVERY SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede solicitar el envío del enlace de recuperación al ingresar su correo electrónico y pulsar el botón "Enviar"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0005, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede establecer una nueva contraseña al completar el formulario y pulsar el botón "Guardar" mediante el enlace enviado a su correo electrónico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROFILE SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la configuración de su identidad y datos personales haciendo clic en la pestaña (tab) "Perfil"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0012, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede hacer clic en el botón “Subir” de la pestaña Perfil de los Ajustes para cargar una imagen de su computadora y usarla como foto de perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0012, RNF0015, RNF0018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede hacer clic en el botón “Quitar” de la pestaña Perfil de los Ajustes para eliminar su foto de perfil actual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede editar su nombre haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede editar su Organización/Institución haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede editar su Sector haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede editar su Rol haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cambiar el idioma de la interfaz de la plataforma haciendo clic en el menú desplegable de Idiomas ubicado pestaña Perfil de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0012, RNF0018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede guardar o descartar las modificaciones realizadas en su información de Perfil a través de los botones de acción ubicados al final de la sección</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0003, RNF0011, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREFERENCES SETTINGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la configuración regional y de visualización haciendo clic en la pestaña (tab) "Preferencias"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar el Tema de la Interfaz haciendo clic en el interruptor de opción entre Claro y Oscuro en la pestaña Preferencias de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar la Zona Horaria/Región de la lista desplegable provista en la pestaña Preferencias de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar la Guía Interactiva haciendo clic en el botón "Repetir Guia Interactiva" en la pestaña Preferencias de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede aplicar, guardar o descartar las modificaciones realizadas en la configuración de Preferencias a través de los botones de acción ubicados al final de la pestaña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOTIFICATIONS SETTINGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la configuración de alertas y comunicaciones haciendo clic en la pestaña (tab) "Notificaciones"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede activar o desactivar la recepción de Notificaciones por Correo Electrónico mediante un interruptor en la pestaña Notificaciones de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede activar o desactivar la recepción de Notificaciones dentro del Portal (In-App) mediante un Interruptor en la pestaña Notificaciones de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede configurar de forma granular los Tipos de Notificación (Recordatorios, Actualizaciones, Facturación, Novedades) para el canal de Correo Electrónico usando checkboxes individuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede configurar de forma granular los Tipos de Notificación  (Recordatorios, Actualizaciones, Facturación, Novedades) para el canal Dentro del Portal (In-App) usando checkboxes individuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar la frecuencia de envío para cada tipo de notificación configurada (Inmediato / Diario / Semanal / Nunca) mediante un menú desplegable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede aplicar, guardar o descartar las modificaciones realizadas en la configuración de Notificaciones a través de los botones de acción ubicados al final de la pestaña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede revertir todos los cambios y restablecer la configuración original del sistema haciendo clic en el botón "Restaurar valores predeterminados" en la pestaña Notificaciones de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECURITY SETTINGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a las herramientas de protección y gestión de cuenta haciendo clic en la pestaña (tab) "Seguridad y Cuenta"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el flujo de cambio de correo electrónico haciendo clic en el enlace o botón "Cambiar Correo Electrónico" en la pestaña Seguridad y Cuenta de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar la nueva dirección de correo electrónico y su Contraseña Actual en los campos requeridos en la pestaña Seguridad y Cuenta de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar la verificación de un nuevo correo electrónico o cancelar el proceso de cambio en la pestaña Seguridad y Cuenta de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe confirmar la nueva dirección haciendo clic en el enlace único de verificación enviado al nuevo correo electrónico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0003, RNF0011, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el flujo de eliminación de cuenta haciendo clic en el enlace o botón "Eliminar Mi Cuenta" en la pestaña Seguridad y Cuenta de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar su Contraseña Actual en el campo de texto provisto dentro de la advertencia de confirmación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0003, RNF0011, RNF0013, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede confirmar o cancelar el proceso de eliminación irreversible de su cuenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el proceso de cambio de contraseña ingresando su Contraseña Actual, la Nueva Contraseña y la Confirmación en los campos requeridos en la pestaña Seguridad y Cuenta de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede ejecutar o cancelar el cambio de contraseña a través del formulario de seguridad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0003, RNF0011, RNF0013, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el proceso de activación/desactivación de la Autenticación en Dos Pasos (2FA) mediante la acción en el interruptor en la pestaña Seguridad y Cuenta de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el proceso de Cierre de Sesión Remota haciendo clic en el botón "Cerrar Sesión en Todos los Dispositivos" en la pestaña Seguridad y Cuenta de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 2 - Gestión de Proyectos y Ciclo de Vida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede hacer clic en el logo “MEUX Lab” para volver a la Pantalla Principal estando dentro del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede hacer clic en el icono de Menú hamburguesa para contraer o abrir el Menú lateral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede escribir en la barra de búsqueda para consultar proyectos creados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede abrir un proyecto haciendo clic en la sugerencia correspondiente dentro de la lista de resultados de búsqueda del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0003, RNF0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede marcar o desmarcar un proyecto como favorito haciendo clic en el ícono de Estrella visible en la tarjeta del proyecto dentro de la lista de resultados de búsqueda del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede borrar su entrada en la barra de búsqueda del Dashboard haciendo clic en el icono de Cancelar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede desplegar y ocultar el Panel de Notificaciones haciendo clic en el ícono de la campana ubicado en el Header del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOTIFICATIONS SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede alternar la vista del historial de notificaciones entre "Todas" y "Leídas" haciendo clic en las pestañas (tabs) correspondientes dentro del panel de notificaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar al recurso o acción relevante haciendo clic en el cuerpo de cualquier notificación dentro del panel de notificaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede abrir el Menú Contextual haciendo clic en el ícono de tres puntos horizontales (Albóndigas) asociado a una notificación individual del panel de notificaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cambiar el estado de lectura de una notificación haciendo clic en la opción "Marcar como leída" o "Marcar como no leída" desde el Menú Contextual del panel de notificaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede eliminar una notificación específica del historial haciendo clic en la opción "Eliminar esta notificación" desde el Menú Contextual del panel de notificaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede marcar todas las notificaciones visibles en la pestaña activa como leídas haciendo clic en el enlace hipertexto "Marcar todas como leídas"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USER MENU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede desplegar el Menú de Administración del Perfil haciendo clic en su Foto de Perfil en el Header del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla Editar Perfil haciendo clic en la opción de “Editar Perfil” en el Menú de Administración del perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Ajustes haciendo clic en la opción de “Ajustes” en el Menú de Administración del Perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Papelera de Reciclaje haciendo clic en la opción de “Papelera” en el Menú lateral en el Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Ayuda haciendo clic en la opción de “Ayuda &amp; Soporte” en el Menú de Administración del Perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Landing Page haciendo clic en la opción de “Cerrar Sesión” en el Menú de Administración del Perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0008, RNF0009, RNF0011, RNF0020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIDEBAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla Principal haciendo clic en la opción “Inicio” del Menú lateral en el Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Proyectos Recientes haciendo clic en la opción “Recientes” del Menú lateral en el Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Proyectos Favoritos haciendo clic en la opción “Favoritos” del Menú lateral en el Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Proyectos Archivados haciendo clic en la opción “Archivados” del Menú lateral en el Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROJECTS VIEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cambiar el formato de presentación de la lista de proyectos del Dashboard haciendo clic en los iconos de "Vista Cuadrícula", "Vista de Lista" o "Vista Kanban"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0003, RNF0011, RNF0012, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede mover un proyecto de una columna a otra mediante la acción de arrastrar y soltar en el modo de vista Kanban del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0003, RNF0011, RNF0015, RNF0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede modificar la secuencia de ordenamiento de los proyectos del Dashboard haciendo clic en la lista desplegable "Ordenar por" y seleccionando un criterio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0003, RNF0011, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede filtrar los proyectos por Método UX haciendo clic en la lista desplegable "Métodos" y seleccionando una o varias opciones en el Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede filtrar los proyectos del Dashboard por Estado haciendo clic en la lista desplegable "Estado" y seleccionando una opción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder al Módulo de Gestión de un proyecto haciendo clic en la tarjeta de proyecto correspondiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar la edición del nombre del proyecto haciendo clic en el nombre dentro de la tarjeta de proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede finalizar la edición del nombre del proyecto pulsando la tecla Enter o haciendo clic fuera del campo de texto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede alternar el estado de Favorito de un proyecto haciendo clic en el ícono de Estrella en la tarjeta del proyecto del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede abrir el Menú Contextual de Gestión haciendo clic en el ícono de tres puntos horizontales (Meatball) en la tarjeta de un proyecto del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder al Módulo de Gestión del proyecto en una nueva pestaña del navegador haciendo clic en la opción "Abrir en una nueva pestaña" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0016, RNF0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el modo de edición del nombre del proyecto haciendo clic en la opción "Cambiar nombre" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede marcar un proyecto como Favorito haciendo clic en la opción "Agregar a Favoritos" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede retirar un proyecto de la lista de Favoritos haciendo clic en la opción "Quitar de Favoritos" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cambiar el estado de un proyecto a "Archivado" haciendo clic en la opción "Archivar" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0013, RNF0015, RNF0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede crear una copia exacta del proyecto haciendo clic en la opción "Duplicar" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Recursos de Distribución haciendo clic en la opción "Compartir" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Análisis y Resultados haciendo clic en la opción "Ver Resultados" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARCHIVED SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede restaurar un proyecto haciendo clic en la opción "Quitar de Archivados" desde el Menú Contextual (disponible en la vista de Archivados)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRASH SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede enviar el proyecto a la Papelera de Reciclaje haciendo clic en la opción "Eliminar" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0009, RNF0010, RNF0011, RNF0013, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede confirmar o cancelar el envío de un proyecto a la Papelera a través del modal de advertencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede buscar proyectos eliminados ingresando texto en el campo de Búsqueda provisto dentro de la Pantalla Papelera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede abrir un Menú Contextual haciendo clic en el ícono de tres puntos horizontales (Albóndigas) para un proyecto específico en la lista de la Pantalla Papelera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede restaurar (recuperar) un proyecto a su ubicación original haciendo clic en la opción "Recuperar" desde el Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede eliminar permanentemente un proyecto haciendo clic en la opción "Eliminar Definitivamente" dentro del Menú Contextual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede confirmar o cancelar la eliminación permanente e irreversible de los proyectos de la Papelera a través del modal de advertencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar la acción de vaciar la Papelera haciendo clic en el botón "Vaciar Papelera" ubicado en el encabezado de la Pantalla Papelera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede ejecutar la eliminación permanente de todos los proyectos haciendo clic en el botón "Confirmar Eliminación Permanente" dentro del pop-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CREATE PROJECT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el proceso de creación de un nuevo proyecto haciendo clic en el botón principal "+ Crear Proyecto" ubicado en el Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0002, RNF0003, RNF0011, RNF0015, RNF0024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar un nombre para el nuevo proyecto haciendo clic y escribiendo en el campo de texto requerido del modal de creación de proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe seleccionar un Método UX haciendo clic en la tarjeta de la opción deseada para completar el formulario del modal de creación de proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede finalizar/cancelar el proceso de Creación Proyecto haciendo clic en el botón "Crear" o “Cancelar” del modal de Creación de proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 3 - Orquestador y Contrato de Módulos (Factory)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal; Módulo de Usabilidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arquitectura Backend (sin pantalla)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe instanciar dinámicamente una implementación concreta de módulo de usabilidad mediante el Factory, según el tipo de método seleccionado al crear el proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe validar que el tipo de módulo solicitado esté registrado en el catálogo del Factory antes de crear el proyecto, rechazando la operación en caso contrario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe inicializar el módulo instanciado antes de habilitar la participación de usuarios finales en el proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todo módulo concreto debe implementar el contrato común de módulo de usabilidad, exponiendo de forma homogénea sus operaciones de inicialización, métricas y validación de datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe validar la estructura de los datos enviados por el participante contra el módulo correspondiente antes de persistir cualquier resultado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0009, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe permitir consultar un resumen de métricas de cualquier proyecto en un formato homogéneo, sin importar el tipo de módulo utilizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe controlar las transiciones de estado del ciclo de vida del proyecto (Edición → Publicado → Finalizado), restringiendo qué acciones son válidas en cada estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe permitir que cada módulo reciba y almacene sus propios parámetros de configuración de forma independiente al Portal, sin que este último conozca su estructura interna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0028, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 4 - Entorno de Participante y Accesibilidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACCESSIBILITY SETTINGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a las opciones de usabilidad (lectores de pantalla, contraste y tamaño de fuente) haciendo clic en la pestaña (tabs) "Accesibilidad"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0011, RNF0012, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar el tamaño de fuente (Pequeño/Mediano/Grande) mediante botones de opción o un deslizador en la pestaña Accesibilidad de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede activar o desactivar el modo de Alto Contraste mediante un interruptor en la pestaña Accesibilidad de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede activar o desactivar la reducción de animaciones de la interfaz mediante un interruptor en la pestaña Accesibilidad de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0012, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede visualizar la lista completa de Atajos de Teclado disponibles haciendo clic en el enlace o botón "Ver Lista" en la pestaña Accesibilidad de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede aplicar, guardar o descartar las modificaciones realizadas en las preferencias de Accesibilidad a través de los botones de acción ubicados al final de la pestaña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAJOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar a la Pantalla Principal (Dashboard) desde cualquier ubicación presionando la combinación de teclas Alt + D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0004, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede abrir el Centro de Ayuda presionando la combinación de teclas Alt + H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la Pantalla de Ajustes (Perfil, Preferencias, etc.) presionando la combinación de teclas Alt +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cerrar la sesión activa presionando la combinación de teclas Alt + Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0008, RNF0009, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede desplegar el Menú del Perfil presionando la combinación de teclas Alt + U</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la Pantalla de Papelera presionando la combinación de teclas Alt + P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede abrir el formulario o modal para la creación de un nuevo proyecto presionando la combinación de teclas Ctrl + N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede activar el foco directo en la barra de búsqueda principal presionando la tecla / (barra) o la combinación Ctrl + F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede alternar cíclicamente entre las diferentes vistas del Dashboard (Lista, Cuadrícula, Kanban) presionando la combinación de teclas Ctrl + L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede moverse verticalmente entre los proyectos seleccionables de la lista o cuadrícula presionando las teclas ↑ (Flecha Arriba) o ↓ (Flecha Abajo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede abrir el proyecto que se encuentra actualmente resaltado o seleccionado presionando la tecla Enter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede marcar o desmarcar el proyecto actualmente seleccionado o abierto como favorito presionando la tecla F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0013, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede archivar el proyecto actualmente seleccionado o abierto presionando la tecla A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el proceso de eliminación del proyecto presionando la tecla Del o la combinación Ctrl + Supr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0010, RNF0013, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar hacia el siguiente elemento interactivo de la interfaz (botones, enlaces, campos de formulario) presionando la tecla Tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar hacia el elemento interactivo anterior de la interfaz (botones, enlaces, campos de formulario) presionando la combinación de teclas Shift + Tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede ejecutar la acción del botón, enlace o campo actualmente enfocado presionando la tecla Enter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cerrar cualquier modal, diálogo, tooltip o menú abierto presionando la tecla Esc (Escape)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede activar el texto descriptivo adicional o tooltip de un elemento actualmente enfocado presionando la combinación de teclas Alt + I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 5 - Motor de Telemetría</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor de Telemetría; Participante; Investigador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe establecer y mantener una conexión WebSocket activa entre el cliente participante y el servidor durante toda la sesión de evaluación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0009, RNF0024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe registrar cada conexión entrante y liberar los recursos asociados automáticamente cuando la sesión finaliza o se pierde la conexión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0021, RNF0024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe capturar los eventos de interacción del participante (foco, posición en el DOM, timestamp) durante la ejecución de la tarea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe procesar cada evento de telemetría recibido y persistirlo junto con sus metadatos en formato JSONB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0009, RNF0025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe transmitir en tiempo real los eventos relevantes de la sesión hacia el panel del investigador conectado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe asociar cada evento de telemetría a su identificador de sesión y marca de tiempo, permitiendo reconstruir cronológicamente la sesión completa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0025, RNF0022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 8 - Monetización y Suscripciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congelada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investigador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREMIUM SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el flujo de actualización de la cuenta haciendo clic en el botón "FREE" ubicado en el Header del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0003, RNF0011, RNF0024, RNF0027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Won't have</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar el plan que quiera al dar click en el botón FREE ubicado en el Header de la página (Etapa 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede confirmar su intención de compra haciendo clic en el botón "Continuar con el Pago" en la Pantalla de Pago (Etapa 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0009, RNF0011, RNF0013, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla Principal haciendo clic en el botón “Cancelar” durante el flujo de pago suscripción en la Pantalla de Pago (Etapa 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0004, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar el método de pago (ej. Tarjeta de Crédito/Débito, PayPal) mediante botones de opciones en la Pantalla de Pago (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar el Número de la Tarjeta en el campo de texto provisto en la Pantalla de Pago (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0006, RNF0009, RNF0011, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar el Nombre Completo tal como aparece en la tarjeta en el campo correspondiente en la Pantalla de Pago (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0009, RNF0011, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe seleccionar la Fecha de Vencimiento (Mes y Año) de la tarjeta usando menús desplegables en la Pantalla de Pago (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar el Código de Seguridad (CVV) en el campo de texto provisto en la Pantalla de Pago (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar la dirección de facturación (Calle, Ciudad, Código Postal, País) en los campos de texto y listas desplegables obligatorios en la Pantalla de Pago (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede ejecutar el pago y la suscripción haciendo clic en el botón "Pagar y Suscribirse" o dar click en el botón Regresar (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0006, RNF0009, RNF0010, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar el ciclo de facturación (ej. Mensual / Anual), lo que actualiza el precio final mostrado en la Pantalla de Pago (Etapa 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Confirmación de Suscripción después de que la pasarela de pago confirma que la transacción fue exitosa en la Pantalla de Pago (Etapa 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0004, RNF0011, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede regresar a la Pantalla Principal haciendo clic en el botón principal "Ir al Dashboard" al finalizar la transacción en la Pantalla de Pago (Etapa 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0004, RNF0011, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la pestaña de gestión de su suscripción haciendo clic en un enlace secundario como "Gestionar Facturación", que lo lleva directamente a la pestaña "Suscripción / Facturación" desde la Pantalla de Pago (Etapa 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREMIUM SETTINGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la gestión de su plan, pagos y facturación haciendo clic en la pestaña (tab) "Suscripción / Facturación"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cambiar el método de pago (ej. actualizar tarjeta) abriendo el formulario de pago simplificado en la pestaña Suscripción / Facturación de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder y descargar el historial de facturación (recibos) en un formato legible en la pestaña Suscripción / Facturación de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el flujo de Cancelación de Suscripción haciendo clic en el botón "Cancelar Suscripción" en la pestaña Suscripción / Facturación de los Ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede confirmar la cancelación definitiva haciendo clic en el botón destructivo "Cancelar Suscripción de Todos Modos"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cancelar el proceso de Cancelación de Suscripción y volver a la pestaña de gestión haciendo clic en el botón "Regresar"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cambiar el ciclo de facturación (ej. de Mensual a Anual) o cambiar el plan haciendo clic en el botón "Cambiar Plan/Ciclo"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 9 - Soporte, Ayuda y Onboarding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar a la Página Principal del Centro de Ayuda haciendo clic en el logo “MEUX Lab | Centro de Ayuda”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001, RNF0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cambiar el idioma de la interfaz de la plataforma haciendo clic en el menú desplegable de Idiomas ubicado en el Header del Centro de Ayuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Reporte haciendo clic en el botón "Contáctenos" ubicado en el Header del Centro de Ayuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIN HELP SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede buscar artículos de apoyo, guías y tutoriales escribiendo en la barra de búsqueda principal de la Pantalla Principal del Centro de Ayuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar a la Página de Listado de Subtemas de una categoría principal haciendo clic en la Tarjeta de Tema correspondiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder al contenido detallado de un artículo haciendo clic en el título de un Subtema de la lista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede saltar a secciones específicas dentro del artículo haciendo clic en los enlaces de la Tabla de Contenidos en el Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar a la fuente externa o al recurso vinculado haciendo clic en los enlaces de hipertexto incluidos en el cuerpo del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0004, RNF0011, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar hacia atrás a cualquier nivel jerárquico superior haciendo clic en cualquiera de los enlaces de la Ruta de Navegación ubicada en la parte superior del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0004, RNF0011, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP SIDEBAR MENU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede expandir y colapsar la lista de Subtemas en la Pantalla Principal del Centro de Ayuda haciendo clic en el título de la Categoría Principal (Tema) en el Menú Lateral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede navegar y visualizar el contenido completo de cualquier Subtema/Artículo de la Pantalla Principal del Centro de Ayuda haciendo clic en el título del elemento expandido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede volver a la parte superior de la página haciendo clic en el ícono de flecha arriba que es visible cuando se encuentra en la parte inferior de un artículo largo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USER HELP SCREEN MENU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede desplegar el Menú de Administración del Perfil haciendo clic en su Foto de Perfil ubicada en el Header del Centro de Ayuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Pantalla de Seguimiento de Soporte haciendo clic en la opción "Mi Actividad" en el Menú de Administración del Perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario es redirigido a la Landing Page y su sesión se cierra haciendo clic en la opción "Cerrar Sesión" en el Menú de Administración del Perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPORT SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar la clasificación de la solicitud (ej. Reporte de Error, Solicitud de Función, Consulta General) antes de llenar el formulario principal de la Pantalla de Reporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario debe ingresar un Asunto conciso y una Descripción detallada de la solicitud en los campos de texto correspondientes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede finalizar y enviar la solicitud al equipo de soporte haciendo clic en el botón "Enviar Solicitud"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVITY SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede filtrar el listado de solicitudes de soporte haciendo clic en las pestañas (tabs) de estado: "Enviado", "En Revisión" y "Contestado"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede acceder a la vista detallada de la descripción del ticket haciendo clic en la tarjeta o fila de una solicitud en el listado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede alternar el ordenamiento del listado (Ascendente/Descendente) haciendo clic en el icono de flechas de ordenamiento ubicado en el encabezado de la columna de fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEEDBACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede cerrar el Formulario de Feedback emergente haciendo clic en el ícono de "Cerrar" (X) en la ventana del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede enviar retroalimentación positiva haciendo clic en el botón "Sí" en el Formulario de feedback emergente en la ventana del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0009, RNF0013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede iniciar el flujo de detalle haciendo clic en el botón "No" en el Formulario de feedback emergente en la ventana del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede seleccionar opciones de clasificación haciendo clic en las opciones disponibles en el Formulario de feedback emergente en la ventana del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003, RNF0011, RNF0013, RNF0014, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede proporcionar comentarios detallados escribiendo en el campo de texto en el Formulario de feedback emergente en la ventana del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0011, RNF0013, RNF0014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede enviar la retroalimentación negativa final haciendo clic en el botón "Enviar" en el Formulario de feedback emergente en la ventana del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede retroceder en el formulario haciendo clic en el ícono de "Flecha Atrás" en el Formulario de feedback emergente en la ventana del Artículo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUTORIAL SCREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede decidir iniciar u omitir la Guía Interactiva después de registrarse desde la Pantalla de Bienvenida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede avanzar al siguiente paso de la Guía Interactiva haciendo clic en el botón "Siguiente" en el tooltip del paso actual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede retroceder al paso anterior haciendo clic en el botón "Anterior" en el tooltip de la Guía Interactiva (disponible a partir del Paso 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario puede finalizar el la Guía Interactiva haciendo clic en el botón "Finalizar Recorrido" y comenzar a usar la aplicación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002, RNF0011, RNF0013, RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total RF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta Prioridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderada Prioridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baja Prioridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribución MoSCoW (Backlog Completo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 6 - Módulos Específicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Épica 7 - Métricas, Reportes e Inteligencia de Datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID RNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre / Resumen</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># RF Asociados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF que lo referencian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La carga inicial completa (renderización y listado de datos) de las vistas principales (Dashboard, Ajustes, Proyectos) debe ser completada en: Menos de 3 segundos para el 90% de las solicitudes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0120, RF0121, RF0122, RF0126, RF0127, RF0020, RF0021, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0052, RF0056, RF0058, RF0077, RF0082, RF0083, RF0084, RF0086, RF00191, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0135, RF0136, RF0137, RF0138, RF0139, RF0140, RF0145, RF0146, RF0147, RF0148, RF0149, RF0152, RF0153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El tiempo de procesamiento de todas las transacciones de escritura (Registro, Login, Creación de Proyecto, Confirmación de Eliminación) debe ser retornado al usuario en: Menos de 2 segundos desde la interacción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0008, RF0012, RF0013, RF0016, RF0017, RF0096, RF0101, RF0108, RF0123, RF0124, RF0125, RF0036, RF0078, RF0079, RF0080, RF0081, RF0084, RF0087, RF00186, RF00188, RF0115, RF0170, RF0178, RF0179, RF0180, RF0059, RF0069, RF0071, RF0144, RF0150, RF0151, RF0154, RF0155, RF0157, RF0161, RF0166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los elementos dinámicos de la interfaz (despliegue de Modales, Menús Contextuales, Tooltips o Pop-ups de confirmación) deben ser mostrados y responder a las interacciones del usuario en: Menos de 200 milisegundos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0014, RF0088, RF0089, RF0090, RF0091, RF0092, RF0093, RF0094, RF0095, RF0096, RF0097, RF0098, RF0099, RF0100, RF0101, RF0102, RF0103, RF0104, RF0105, RF0106, RF0107, RF0108, RF0109, RF0116, RF0117, RF0118, RF00119, RF0120, RF0121, RF0122, RF0123, RF0124, RF0125, RF0126, RF0127, RF0019, RF0020, RF0021, RF0022, RF0023, RF0024, RF0025, RF0026, RF0027, RF0028, RF0029, RF0030, RF0031, RF0032, RF0033, RF0034, RF0035, RF0037, RF0038, RF0039, RF0040, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0049, RF0050, RF0051, RF0052, RF0053, RF0054, RF0055, RF0056, RF0057, RF0058, RF0074, RF0075, RF0076, RF0077, RF0078, RF0079, RF0080, RF0081, RF0082, RF0083, RF0084, RF0085, RF0086, RF0087, RF0113, RF0115, RF0167, RF0168, RF0169, RF0171, RF0172, RF0173, RF0174, RF0175, RF0176, RF0177, RF0181, RF0182, RF0183, RF0184, RF0185, RF00195, RF00197, RF0059, RF0060, RF0061, RF0062, RF0063, RF0070, RF0072, RF0073, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0136, RF0137, RF0138, RF0139, RF0140, RF0141, RF0143, RF0144, RF0145, RF0146, RF0147, RF0148, RF0149, RF0150, RF0151, RF0152, RF0153, RF0154, RF0155, RF0156, RF0158, RF0159, RF0162, RF0163, RF0164, RF0165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El tiempo transcurrido desde que se hace clic en un enlace de navegación hasta que la nueva página comienza a cargarse debe ser de: Menos de 1 segundo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0002, RF0003, RF0004, RF0005, RF0006, RF0007, RF0015, RF0018, RF0167, RF0168, RF0169, RF0172, RF0177, RF0062, RF0071, RF0072, RF0073, RF0142, RF0143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las solicitudes a procesos secundarios (ej. reenvío de correos, generación de reportes ligeros) deben ser procesadas y el feedback mostrado al usuario en: Menos de 5 segundos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todas las contraseñas de usuario deben ser almacenadas y procesadas utilizando métodos criptográficos seguros: Utilizar un algoritmo de hashing unidireccional (ej. bcrypt o Argon2) con un factor de salting único y aleatorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0008, RF0012, RF0013, RF0017, RF0064, RF0067, RF0069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe monitorear y restringir los intentos fallidos de inicio de sesión: Bloquear temporalmente la cuenta o la dirección IP por 30 minutos después de 5 intentos fallidos de contraseña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe invalidar inmediatamente todas las sesiones activas, excepto la actual, al confirmarse la acción de "Cerrar Sesión en Todos los Dispositivos": Invalidación en tiempo real de los tokens de sesión remota al ejecutar el RF de cierre de sesión remota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0036, RF0170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toda la comunicación de datos entre el navegador del usuario y el servidor (incluyendo login, formularios y solicitudes a API) debe ser cifrada: Utilizar el protocolo HTTPS/TLS 1.2 o superior de extremo a extremo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0008, RF0011, RF0012, RF0013, RF0017, RF0036, RF0075, RF00190, RF0170, RF00193, RF00195, RF00196, RF00197, RF0061, RF0063, RF0064, RF0065, RF0066, RF0067, RF0068, RF0069, RF0157, RF0161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al confirmar la "Eliminación Permanente de Cuenta" o "Eliminación Definitiva de Proyectos", los datos asociados deben ser marcados para borrado y retirados del almacenamiento: Eliminación lógica e irreversible de todos los datos personales y de proyecto en un plazo máximo de 72 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0075, RF0180, RF0069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todos los elementos de la interfaz (header, footer, botones, formularios, paleta de colores y tipografía) deben ser uniformes y coherentes en todas las vistas, desde la Landing Page hasta las pantallas internas de la aplicación. Cumplir al 100% con la guía de estilo y el branding definidos en el Design System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0001, RF0002, RF0003, RF0004, RF0005, RF0006, RF0007, RF0008, RF0009, RF0010, RF0011, RF0014, RF0015, RF0088, RF0089, RF0090, RF0091, RF0092, RF0093, RF0094, RF0095, RF0096, RF0097, RF0098, RF0099, RF0100, RF0101, RF0102, RF0103, RF0104, RF0105, RF0106, RF0107, RF0108, RF0109, RF0116, RF0117, RF0118, RF00119, RF0120, RF0121, RF0122, RF0123, RF0124, RF0125, RF0126, RF0127, RF0018, RF0019, RF0020, RF0021, RF0022, RF0023, RF0024, RF0025, RF0026, RF0027, RF0028, RF0029, RF0030, RF0031, RF0032, RF0033, RF0034, RF0035, RF0036, RF0037, RF0038, RF0039, RF0040, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0049, RF0050, RF0051, RF0052, RF0053, RF0054, RF0055, RF0056, RF0057, RF0058, RF0074, RF0075, RF0076, RF0077, RF0078, RF0079, RF0080, RF0081, RF0082, RF0083, RF0084, RF0085, RF0086, RF0087, RF0110, RF0111, RF0112, RF0113, RF0114, RF0115, RF0175, RF0176, RF0185, RF0059, RF0060, RF0061, RF0063, RF0064, RF0065, RF0066, RF0067, RF0068, RF0070, RF0071, RF0072, RF0073, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0135, RF0136, RF0137, RF0138, RF0139, RF0140, RF0141, RF0142, RF0143, RF0144, RF0145, RF0146, RF0147, RF0148, RF0149, RF0150, RF0151, RF0152, RF0153, RF0154, RF0155, RF0158, RF0159, RF0160, RF0163, RF0164, RF0165, RF0166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El diseño de la aplicación debe ajustarse dinámicamente para mantener la funcionalidad, legibilidad y estética: Funcionalidad y usabilidad completas en resoluciones desde 320px (móvil) hasta 1920px (escritorio), sin necesidad de scroll horizontal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0001, RF0002, RF0003, RF0004, RF0005, RF0006, RF0007, RF0088, RF0089, RF0095, RF0097, RF0098, RF0099, RF0100, RF0102, RF0103, RF0104, RF0105, RF0106, RF0107, RF0116, RF0117, RF0118, RF00119, RF0018, RF0019, RF0031, RF0032, RF0033, RF0034, RF0035, RF0037, RF0038, RF0039, RF0040, RF0041, RF0057, RF0058, RF0110, RF0111, RF0112, RF0113, RF0114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe proporcionar feedback visual y textual inmediato al usuario tras cualquier interacción (positiva, negativa o neutra): Mostrar mensajes de confirmación de éxito (ej. "Contraseña Actualizada"), advertencias, y mensajes de error claros y accionables (código y descripción)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0014, RF0015, RF0016, RF0090, RF0091, RF0092, RF0093, RF0094, RF0096, RF0101, RF0108, RF0109, RF0120, RF0121, RF0122, RF0123, RF0124, RF0125, RF0126, RF0127, RF0020, RF0024, RF0025, RF0026, RF0028, RF0029, RF0030, RF0047, RF0048, RF0052, RF0055, RF0056, RF0074, RF0075, RF0076, RF0077, RF0078, RF0079, RF0080, RF0081, RF0082, RF0083, RF0085, RF0087, RF00187, RF00190, RF00192, RF00199, RF0115, RF0178, RF0179, RF0180, RF0060, RF0061, RF0063, RF0064, RF0065, RF0066, RF0067, RF0068, RF0069, RF0071, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0136, RF0137, RF0138, RF0139, RF0140, RF0144, RF0145, RF0146, RF0147, RF0148, RF0149, RF0150, RF0151, RF0152, RF0153, RF0154, RF0155, RF0157, RF0158, RF0159, RF0160, RF0161, RF0163, RF0164, RF0166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La funcionalidad clave de la aplicación debe ser accesible y operable sin el uso del mouse, incluyendo la navegación entre elementos, la activación de botones y el cierre de modales: Cumplir con el estándar WCAG 2.1 Nivel A y garantizar la operación completa mediante las teclas Tab, Shift+Tab y Esc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0110, RF0111, RF0112, RF0113, RF0114, RF0167, RF0168, RF0169, RF0170, RF0171, RF0172, RF0173, RF0174, RF0175, RF0176, RF0177, RF0178, RF0179, RF0180, RF0181, RF0182, RF0183, RF0184, RF0185, RF0141, RF0143, RF0156, RF0159, RF0160, RF0162, RF0164, RF0165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todos los patrones de interacción definidos (ej. arrastrar y soltar, tooltips, modales de confirmación) deben comportarse de forma predecible y consistente a lo largo de toda la aplicación. El uso de la tecla Esc debe cerrar cualquier ventana emergente, menú contextual o tooltip activo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0001, RF0014, RF0088, RF0089, RF0090, RF0091, RF0092, RF0093, RF0094, RF0100, RF0109, RF0122, RF0125, RF0019, RF0022, RF0023, RF0024, RF0025, RF0027, RF0029, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0049, RF0050, RF0052, RF0053, RF0054, RF0055, RF0056, RF0057, RF0058, RF0074, RF0075, RF0076, RF0078, RF0079, RF0084, RF0085, RF0086, RF0087, RF0110, RF0111, RF0112, RF0113, RF0114, RF0167, RF0168, RF0169, RF0170, RF0171, RF0172, RF0173, RF0174, RF0175, RF0176, RF0177, RF0178, RF0179, RF0180, RF0181, RF0182, RF0183, RF0184, RF0185, RF0060, RF0061, RF0062, RF0063, RF0070, RF0072, RF0073, RF0131, RF0133, RF0136, RF0138, RF0141, RF0142, RF0143, RF0149, RF0154, RF0155, RF0156, RF0158, RF0159, RF0162, RF0163, RF0164, RF0165, RF0166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La aplicación debe garantizar funcionalidad completa y rendimiento óptimo en los navegadores más utilizados: Soporte total para las dos últimas versiones estables de Google Chrome, Mozilla Firefox, Apple Safari y Microsoft Edge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La interfaz debe mantener la coherencia visual y la funcionalidad en diferentes plataformas de escritorio y móviles: Soporte total para las dos últimas versiones principales de Windows, macOS, Android (Chrome) e iOS (Safari)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La aplicación debe adherirse a los estándares web actuales para garantizar la interoperabilidad y el rendimiento a largo plazo: Todo el código front-end debe ser válido según los estándares HTML5, CSS3 y JavaScript ES6 o superior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0089, RF0095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La aplicación debe ser completamente funcional y legible incluso en las resoluciones de pantalla más pequeñas utilizadas por el mercado objetivo: Soporte completo para una resolución mínima de 360px de ancho en dispositivos móviles y 1280x720 en escritorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0055, RF0074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe estar accesible y completamente funcional para los usuarios finales: Garantizar una disponibilidad (uptime) mínima del 99.9% durante el horario de servicio (24/7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En caso de fallo de un componente no crítico (ej. microservicio secundario), el sistema debe mantener la funcionalidad clave (login, creación y edición de proyectos): Mantener la operación de las funciones críticas sin degradación de rendimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0042, RF00188, RF00194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se debe realizar una copia de seguridad completa de la base de datos de forma periódica: Realizar un backup completo diariamente y almacenarlo fuera del sitio por un mínimo de 7 días</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En caso de un fallo catastrófico (ej. caída completa del servidor principal), el sistema debe ser capaz de restaurar la operación: El tiempo de recuperación total (RTO) no debe exceder las 4 horas desde la detección del fallo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">— SIN COBERTURA —</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe mantener los umbrales de rendimiento definidos (carga &lt;3s, transacción &lt;2s) al operar simultáneamente: Soportar eficientemente 500 usuarios concurrentes activos en la plataforma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0084, RF00193, RF00194, RF0059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La arquitectura de la base de datos debe ser capaz de gestionar un volumen creciente de datos de proyecto sin degradación del rendimiento: Soportar un crecimiento de datos del 30% anual manteniendo los tiempos de respuesta definidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00196, RF00198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe permitir a cada usuario individual crear y gestionar un número considerable de proyectos: Permitir la creación y gestión de 100 proyectos activos por usuario sin experimentar degradación en la carga del Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENDIENTE — depende del modelo de suscripción (Épica 8, congelada). No es un olvido: se resolverá cuando se desarrolle Épica 8.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La infraestructura de hosting debe estar dimensionada para manejar picos de tráfico inducidos por campañas o lanzamientos: Soportar el doble del tráfico promedio diario durante períodos sostenidos de hasta 6 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todo el código desarrollado debe seguir un estándar de codificación consistente y ser documentado con comentarios y guías para facilitar su mantenimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF00186, RF00189, RF00191, RF00199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF0029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema debe incluir enlaces visibles y accesibles a la Política de Privacidad y los Términos y Condiciones, los cuales deben ser aceptados durante el flujo de registro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF0008, RF0009, RF0010, RF0011</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="620">
+  <si>
+    <t>ID RF</t>
+  </si>
+  <si>
+    <t>Épica</t>
+  </si>
+  <si>
+    <t>Estado Épica</t>
+  </si>
+  <si>
+    <t>Actor(es)</t>
+  </si>
+  <si>
+    <t>Origen (Pantalla)</t>
+  </si>
+  <si>
+    <t>Descripción del RF</t>
+  </si>
+  <si>
+    <t>RNF Relacionados</t>
+  </si>
+  <si>
+    <t>Estatus</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Dificultad</t>
+  </si>
+  <si>
+    <t>Fase</t>
+  </si>
+  <si>
+    <t>Versión</t>
+  </si>
+  <si>
+    <t>MoSCoW</t>
+  </si>
+  <si>
+    <t>RF0001</t>
+  </si>
+  <si>
+    <t>Épica 1 - Núcleo y Seguridad</t>
+  </si>
+  <si>
+    <t>Activa</t>
+  </si>
+  <si>
+    <t>Investigador; Portal</t>
+  </si>
+  <si>
+    <t>ONBOARDING SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar a la siguiente pantalla de información en la Pantalla de Bienvenida (Onboarding) deslizando la pantalla hacia la izquierda o haciendo clic en icono de flecha, permitiendo la visualización secuencial de las características clave</t>
+  </si>
+  <si>
+    <t>RNF0011, RNF0012, RNF0015</t>
+  </si>
+  <si>
+    <t>Propuesto</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>Could have</t>
+  </si>
+  <si>
+    <t>RF0002</t>
+  </si>
+  <si>
+    <t>LANDING PAGE</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Registro haciendo clic en el botón de "Registrarse" ubicado en el Header de la Landing Page</t>
+  </si>
+  <si>
+    <t>RNF0004, RNF0011, RNF0012</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Must have</t>
+  </si>
+  <si>
+    <t>RF0003</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Inicio de sesión haciendo clic en el botón de "Iniciar Sesión" ubicado en el Header de la Landing Page</t>
+  </si>
+  <si>
+    <t>RF0004</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Inicio de sesión haciendo clic en el botón “Empieza Ya” ubicado al final de la Landing Page</t>
+  </si>
+  <si>
+    <t>Moderada</t>
+  </si>
+  <si>
+    <t>Should have</t>
+  </si>
+  <si>
+    <t>RF0005</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Registro haciendo clic en el enlace hipertexto “¿No tienes cuenta? Regístrate” para completar el formulario de registro</t>
+  </si>
+  <si>
+    <t>RF0006</t>
+  </si>
+  <si>
+    <t>El usuario puede hacer clic en el logo “MEUX Lab” para regresar a la Landing Page desde la Pantalla de Registro/Inicio de Sesión</t>
+  </si>
+  <si>
+    <t>RF0007</t>
+  </si>
+  <si>
+    <t>SIGN UP SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Inicio de sesión haciendo clic en el enlace hipertexto “¿Ya tienes cuenta? Inicia sesión” para introducir sus credenciales</t>
+  </si>
+  <si>
+    <t>RF0008</t>
+  </si>
+  <si>
+    <t>El usuario completa un formulario en la Pantalla de Registro llenando los campos correspondientes y pulsa el botón de “Registrar” para crear una cuenta</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0006, RNF0009, RNF0011, RNF0029</t>
+  </si>
+  <si>
+    <t>RF0009</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Términos y Condiciones haciendo clic en el enlace de hipertexto ubicado al final del formulario de la Pantalla de Registro</t>
+  </si>
+  <si>
+    <t>RNF0011, RNF0029</t>
+  </si>
+  <si>
+    <t>RF0010</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Políticas de Privacidad haciendo clic en el enlace de hipertexto ubicado al final del formulario de la Pantalla de Registro</t>
+  </si>
+  <si>
+    <t>RF0011</t>
+  </si>
+  <si>
+    <t>El usuario debe marcar la casilla de aceptación para los Términos y Condiciones y la Política de Privacidad en el formulario de la Pantalla de Registro para crear una cuenta</t>
+  </si>
+  <si>
+    <t>RNF0009, RNF0011, RNF0029</t>
+  </si>
+  <si>
+    <t>RF0012</t>
+  </si>
+  <si>
+    <t>LOGIN SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario introduce sus credenciales en la Pantalla de Inicio de Sesión llenando los campos correspondientes y pulsa el botón de “Iniciar Sesión” para ingresar</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0006, RNF0007, RNF0009</t>
+  </si>
+  <si>
+    <t>RF0013</t>
+  </si>
+  <si>
+    <t>El usuario puede pulsar el botón “Inicio de sesión con Google” para ingresar mediante cuentas de Google</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0006, RNF0009</t>
+  </si>
+  <si>
+    <t>RF0014</t>
+  </si>
+  <si>
+    <t>El usuario puede alternar la visibilidad de la contraseña haciendo clic en el ícono de Ojo dentro del campo de entrada de contraseña</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0013, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0015</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el proceso de recuperación de contraseña haciendo clic en el enlace hipertexto “¿Olvidaste la contraseña?”</t>
+  </si>
+  <si>
+    <t>RNF0004, RNF0011, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0016</t>
+  </si>
+  <si>
+    <t>PASSWORD RECOVERY SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede solicitar el envío del enlace de recuperación al ingresar su correo electrónico y pulsar el botón "Enviar"</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0005, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0017</t>
+  </si>
+  <si>
+    <t>El usuario puede establecer una nueva contraseña al completar el formulario y pulsar el botón "Guardar" mediante el enlace enviado a su correo electrónico</t>
+  </si>
+  <si>
+    <t>RF0088</t>
+  </si>
+  <si>
+    <t>PROFILE SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la configuración de su identidad y datos personales haciendo clic en la pestaña (tab) "Perfil"</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0012, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0089</t>
+  </si>
+  <si>
+    <t>El usuario puede hacer clic en el botón “Subir” de la pestaña Perfil de los Ajustes para cargar una imagen de su computadora y usarla como foto de perfil</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0012, RNF0015, RNF0018</t>
+  </si>
+  <si>
+    <t>RF0090</t>
+  </si>
+  <si>
+    <t>El usuario puede hacer clic en el botón “Quitar” de la pestaña Perfil de los Ajustes para eliminar su foto de perfil actual</t>
+  </si>
+  <si>
+    <t>RF0091</t>
+  </si>
+  <si>
+    <t>El usuario puede editar su nombre haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0092</t>
+  </si>
+  <si>
+    <t>El usuario puede editar su Organización/Institución haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0093</t>
+  </si>
+  <si>
+    <t>El usuario puede editar su Sector haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0094</t>
+  </si>
+  <si>
+    <t>El usuario puede editar su Rol haciendo clic en el campo correspondiente de la pestaña Perfil de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0095</t>
+  </si>
+  <si>
+    <t>El usuario puede cambiar el idioma de la interfaz de la plataforma haciendo clic en el menú desplegable de Idiomas ubicado pestaña Perfil de los Ajustes</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0012, RNF0018</t>
+  </si>
+  <si>
+    <t>RF0096</t>
+  </si>
+  <si>
+    <t>El usuario puede guardar o descartar las modificaciones realizadas en su información de Perfil a través de los botones de acción ubicados al final de la sección</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0003, RNF0011, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0097</t>
+  </si>
+  <si>
+    <t>PREFERENCES SETTINGS</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la configuración regional y de visualización haciendo clic en la pestaña (tab) "Preferencias"</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0012</t>
+  </si>
+  <si>
+    <t>RF0098</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar el Tema de la Interfaz haciendo clic en el interruptor de opción entre Claro y Oscuro en la pestaña Preferencias de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0099</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar la Zona Horaria/Región de la lista desplegable provista en la pestaña Preferencias de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0100</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar la Guía Interactiva haciendo clic en el botón "Repetir Guia Interactiva" en la pestaña Preferencias de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0101</t>
+  </si>
+  <si>
+    <t>El usuario puede aplicar, guardar o descartar las modificaciones realizadas en la configuración de Preferencias a través de los botones de acción ubicados al final de la pestaña</t>
+  </si>
+  <si>
+    <t>RF0102</t>
+  </si>
+  <si>
+    <t>NOTIFICATIONS SETTINGS</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la configuración de alertas y comunicaciones haciendo clic en la pestaña (tab) "Notificaciones"</t>
+  </si>
+  <si>
+    <t>RF0103</t>
+  </si>
+  <si>
+    <t>El usuario puede activar o desactivar la recepción de Notificaciones por Correo Electrónico mediante un interruptor en la pestaña Notificaciones de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0104</t>
+  </si>
+  <si>
+    <t>El usuario puede activar o desactivar la recepción de Notificaciones dentro del Portal (In-App) mediante un Interruptor en la pestaña Notificaciones de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0105</t>
+  </si>
+  <si>
+    <t>El usuario puede configurar de forma granular los Tipos de Notificación (Recordatorios, Actualizaciones, Facturación, Novedades) para el canal de Correo Electrónico usando checkboxes individuales</t>
+  </si>
+  <si>
+    <t>RF0106</t>
+  </si>
+  <si>
+    <t>El usuario puede configurar de forma granular los Tipos de Notificación  (Recordatorios, Actualizaciones, Facturación, Novedades) para el canal Dentro del Portal (In-App) usando checkboxes individuales</t>
+  </si>
+  <si>
+    <t>RF0107</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar la frecuencia de envío para cada tipo de notificación configurada (Inmediato / Diario / Semanal / Nunca) mediante un menú desplegable</t>
+  </si>
+  <si>
+    <t>RF0108</t>
+  </si>
+  <si>
+    <t>El usuario puede aplicar, guardar o descartar las modificaciones realizadas en la configuración de Notificaciones a través de los botones de acción ubicados al final de la pestaña</t>
+  </si>
+  <si>
+    <t>RF0109</t>
+  </si>
+  <si>
+    <t>El usuario puede revertir todos los cambios y restablecer la configuración original del sistema haciendo clic en el botón "Restaurar valores predeterminados" en la pestaña Notificaciones de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0116</t>
+  </si>
+  <si>
+    <t>SECURITY SETTINGS</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a las herramientas de protección y gestión de cuenta haciendo clic en la pestaña (tab) "Seguridad y Cuenta"</t>
+  </si>
+  <si>
+    <t>RF0117</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el flujo de cambio de correo electrónico haciendo clic en el enlace o botón "Cambiar Correo Electrónico" en la pestaña Seguridad y Cuenta de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0118</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar la nueva dirección de correo electrónico y su Contraseña Actual en los campos requeridos en la pestaña Seguridad y Cuenta de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF00119</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar la verificación de un nuevo correo electrónico o cancelar el proceso de cambio en la pestaña Seguridad y Cuenta de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0120</t>
+  </si>
+  <si>
+    <t>El usuario debe confirmar la nueva dirección haciendo clic en el enlace único de verificación enviado al nuevo correo electrónico</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0003, RNF0011, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0121</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el flujo de eliminación de cuenta haciendo clic en el enlace o botón "Eliminar Mi Cuenta" en la pestaña Seguridad y Cuenta de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0122</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar su Contraseña Actual en el campo de texto provisto dentro de la advertencia de confirmación</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0003, RNF0011, RNF0013, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0123</t>
+  </si>
+  <si>
+    <t>El usuario puede confirmar o cancelar el proceso de eliminación irreversible de su cuenta</t>
+  </si>
+  <si>
+    <t>RF0124</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el proceso de cambio de contraseña ingresando su Contraseña Actual, la Nueva Contraseña y la Confirmación en los campos requeridos en la pestaña Seguridad y Cuenta de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0125</t>
+  </si>
+  <si>
+    <t>El usuario puede ejecutar o cancelar el cambio de contraseña a través del formulario de seguridad.</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0003, RNF0011, RNF0013, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0126</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el proceso de activación/desactivación de la Autenticación en Dos Pasos (2FA) mediante la acción en el interruptor en la pestaña Seguridad y Cuenta de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0127</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el proceso de Cierre de Sesión Remota haciendo clic en el botón "Cerrar Sesión en Todos los Dispositivos" en la pestaña Seguridad y Cuenta de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0018</t>
+  </si>
+  <si>
+    <t>Épica 2 - Gestión de Proyectos y Ciclo de Vida</t>
+  </si>
+  <si>
+    <t>HOME SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede hacer clic en el logo “MEUX Lab” para volver a la Pantalla Principal estando dentro del Dashboard</t>
+  </si>
+  <si>
+    <t>RF0019</t>
+  </si>
+  <si>
+    <t>El usuario puede hacer clic en el icono de Menú hamburguesa para contraer o abrir el Menú lateral</t>
+  </si>
+  <si>
+    <t>RF0020</t>
+  </si>
+  <si>
+    <t>El usuario puede escribir en la barra de búsqueda para consultar proyectos creados</t>
+  </si>
+  <si>
+    <t>RF0021</t>
+  </si>
+  <si>
+    <t>El usuario puede abrir un proyecto haciendo clic en la sugerencia correspondiente dentro de la lista de resultados de búsqueda del Dashboard</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0003, RNF0011</t>
+  </si>
+  <si>
+    <t>RF0022</t>
+  </si>
+  <si>
+    <t>El usuario puede marcar o desmarcar un proyecto como favorito haciendo clic en el ícono de Estrella visible en la tarjeta del proyecto dentro de la lista de resultados de búsqueda del Dashboard</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0023</t>
+  </si>
+  <si>
+    <t>El usuario puede borrar su entrada en la barra de búsqueda del Dashboard haciendo clic en el icono de Cancelar</t>
+  </si>
+  <si>
+    <t>RF0024</t>
+  </si>
+  <si>
+    <t>El usuario puede desplegar y ocultar el Panel de Notificaciones haciendo clic en el ícono de la campana ubicado en el Header del Dashboard</t>
+  </si>
+  <si>
+    <t>RF0025</t>
+  </si>
+  <si>
+    <t>NOTIFICATIONS SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede alternar la vista del historial de notificaciones entre "Todas" y "Leídas" haciendo clic en las pestañas (tabs) correspondientes dentro del panel de notificaciones</t>
+  </si>
+  <si>
+    <t>RF0026</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar al recurso o acción relevante haciendo clic en el cuerpo de cualquier notificación dentro del panel de notificaciones</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0027</t>
+  </si>
+  <si>
+    <t>El usuario puede abrir el Menú Contextual haciendo clic en el ícono de tres puntos horizontales (Albóndigas) asociado a una notificación individual del panel de notificaciones</t>
+  </si>
+  <si>
+    <t>RF0028</t>
+  </si>
+  <si>
+    <t>El usuario puede cambiar el estado de lectura de una notificación haciendo clic en la opción "Marcar como leída" o "Marcar como no leída" desde el Menú Contextual del panel de notificaciones</t>
+  </si>
+  <si>
+    <t>RF0029</t>
+  </si>
+  <si>
+    <t>El usuario puede eliminar una notificación específica del historial haciendo clic en la opción "Eliminar esta notificación" desde el Menú Contextual del panel de notificaciones</t>
+  </si>
+  <si>
+    <t>RF0030</t>
+  </si>
+  <si>
+    <t>El usuario puede marcar todas las notificaciones visibles en la pestaña activa como leídas haciendo clic en el enlace hipertexto "Marcar todas como leídas"</t>
+  </si>
+  <si>
+    <t>RF0031</t>
+  </si>
+  <si>
+    <t>USER MENU</t>
+  </si>
+  <si>
+    <t>El usuario puede desplegar el Menú de Administración del Perfil haciendo clic en su Foto de Perfil en el Header del Dashboard</t>
+  </si>
+  <si>
+    <t>RF0032</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla Editar Perfil haciendo clic en la opción de “Editar Perfil” en el Menú de Administración del perfil</t>
+  </si>
+  <si>
+    <t>RF0033</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Ajustes haciendo clic en la opción de “Ajustes” en el Menú de Administración del Perfil</t>
+  </si>
+  <si>
+    <t>RF0034</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Papelera de Reciclaje haciendo clic en la opción de “Papelera” en el Menú lateral en el Dashboard</t>
+  </si>
+  <si>
+    <t>RF0035</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Ayuda haciendo clic en la opción de “Ayuda &amp; Soporte” en el Menú de Administración del Perfil</t>
+  </si>
+  <si>
+    <t>RF0036</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Landing Page haciendo clic en la opción de “Cerrar Sesión” en el Menú de Administración del Perfil</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0008, RNF0009, RNF0011, RNF0020</t>
+  </si>
+  <si>
+    <t>RF0037</t>
+  </si>
+  <si>
+    <t>SIDEBAR</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla Principal haciendo clic en la opción “Inicio” del Menú lateral en el Dashboard</t>
+  </si>
+  <si>
+    <t>RF0038</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Proyectos Recientes haciendo clic en la opción “Recientes” del Menú lateral en el Dashboard</t>
+  </si>
+  <si>
+    <t>RF0039</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Proyectos Favoritos haciendo clic en la opción “Favoritos” del Menú lateral en el Dashboard</t>
+  </si>
+  <si>
+    <t>RF0040</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Proyectos Archivados haciendo clic en la opción “Archivados” del Menú lateral en el Dashboard</t>
+  </si>
+  <si>
+    <t>RF0041</t>
+  </si>
+  <si>
+    <t>PROJECTS VIEW</t>
+  </si>
+  <si>
+    <t>El usuario puede cambiar el formato de presentación de la lista de proyectos del Dashboard haciendo clic en los iconos de "Vista Cuadrícula", "Vista de Lista" o "Vista Kanban"</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0003, RNF0011, RNF0012, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0042</t>
+  </si>
+  <si>
+    <t>El usuario puede mover un proyecto de una columna a otra mediante la acción de arrastrar y soltar en el modo de vista Kanban del Dashboard</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0003, RNF0011, RNF0015, RNF0021</t>
+  </si>
+  <si>
+    <t>RF0043</t>
+  </si>
+  <si>
+    <t>El usuario puede modificar la secuencia de ordenamiento de los proyectos del Dashboard haciendo clic en la lista desplegable "Ordenar por" y seleccionando un criterio</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0003, RNF0011, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0044</t>
+  </si>
+  <si>
+    <t>El usuario puede filtrar los proyectos por Método UX haciendo clic en la lista desplegable "Métodos" y seleccionando una o varias opciones en el Dashboard</t>
+  </si>
+  <si>
+    <t>RF0045</t>
+  </si>
+  <si>
+    <t>El usuario puede filtrar los proyectos del Dashboard por Estado haciendo clic en la lista desplegable "Estado" y seleccionando una opción</t>
+  </si>
+  <si>
+    <t>RF0046</t>
+  </si>
+  <si>
+    <t>MAIN</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder al Módulo de Gestión de un proyecto haciendo clic en la tarjeta de proyecto correspondiente</t>
+  </si>
+  <si>
+    <t>RF0047</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar la edición del nombre del proyecto haciendo clic en el nombre dentro de la tarjeta de proyecto</t>
+  </si>
+  <si>
+    <t>RF0048</t>
+  </si>
+  <si>
+    <t>El usuario puede finalizar la edición del nombre del proyecto pulsando la tecla Enter o haciendo clic fuera del campo de texto</t>
+  </si>
+  <si>
+    <t>RF0049</t>
+  </si>
+  <si>
+    <t>El usuario puede alternar el estado de Favorito de un proyecto haciendo clic en el ícono de Estrella en la tarjeta del proyecto del Dashboard</t>
+  </si>
+  <si>
+    <t>RF0050</t>
+  </si>
+  <si>
+    <t>El usuario puede abrir el Menú Contextual de Gestión haciendo clic en el ícono de tres puntos horizontales (Meatball) en la tarjeta de un proyecto del Dashboard</t>
+  </si>
+  <si>
+    <t>RF0051</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder al Módulo de Gestión del proyecto en una nueva pestaña del navegador haciendo clic en la opción "Abrir en una nueva pestaña" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0016, RNF0017</t>
+  </si>
+  <si>
+    <t>RF0052</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el modo de edición del nombre del proyecto haciendo clic en la opción "Cambiar nombre" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0053</t>
+  </si>
+  <si>
+    <t>El usuario puede marcar un proyecto como Favorito haciendo clic en la opción "Agregar a Favoritos" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0054</t>
+  </si>
+  <si>
+    <t>El usuario puede retirar un proyecto de la lista de Favoritos haciendo clic en la opción "Quitar de Favoritos" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0055</t>
+  </si>
+  <si>
+    <t>El usuario puede cambiar el estado de un proyecto a "Archivado" haciendo clic en la opción "Archivar" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0013, RNF0015, RNF0019</t>
+  </si>
+  <si>
+    <t>RF0056</t>
+  </si>
+  <si>
+    <t>El usuario puede crear una copia exacta del proyecto haciendo clic en la opción "Duplicar" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0057</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Recursos de Distribución haciendo clic en la opción "Compartir" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0058</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Análisis y Resultados haciendo clic en la opción "Ver Resultados" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0074</t>
+  </si>
+  <si>
+    <t>ARCHIVED SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede restaurar un proyecto haciendo clic en la opción "Quitar de Archivados" desde el Menú Contextual (disponible en la vista de Archivados)</t>
+  </si>
+  <si>
+    <t>RF0075</t>
+  </si>
+  <si>
+    <t>TRASH SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede enviar el proyecto a la Papelera de Reciclaje haciendo clic en la opción "Eliminar" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0009, RNF0010, RNF0011, RNF0013, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0076</t>
+  </si>
+  <si>
+    <t>El usuario puede confirmar o cancelar el envío de un proyecto a la Papelera a través del modal de advertencia</t>
+  </si>
+  <si>
+    <t>RF0077</t>
+  </si>
+  <si>
+    <t>El usuario puede buscar proyectos eliminados ingresando texto en el campo de Búsqueda provisto dentro de la Pantalla Papelera</t>
+  </si>
+  <si>
+    <t>RF0078</t>
+  </si>
+  <si>
+    <t>El usuario puede abrir un Menú Contextual haciendo clic en el ícono de tres puntos horizontales (Albóndigas) para un proyecto específico en la lista de la Pantalla Papelera</t>
+  </si>
+  <si>
+    <t>RF0079</t>
+  </si>
+  <si>
+    <t>El usuario puede restaurar (recuperar) un proyecto a su ubicación original haciendo clic en la opción "Recuperar" desde el Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0080</t>
+  </si>
+  <si>
+    <t>El usuario puede eliminar permanentemente un proyecto haciendo clic en la opción "Eliminar Definitivamente" dentro del Menú Contextual</t>
+  </si>
+  <si>
+    <t>RF0081</t>
+  </si>
+  <si>
+    <t>El usuario puede confirmar o cancelar la eliminación permanente e irreversible de los proyectos de la Papelera a través del modal de advertencia</t>
+  </si>
+  <si>
+    <t>RF0082</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar la acción de vaciar la Papelera haciendo clic en el botón "Vaciar Papelera" ubicado en el encabezado de la Pantalla Papelera</t>
+  </si>
+  <si>
+    <t>RF0083</t>
+  </si>
+  <si>
+    <t>El usuario puede ejecutar la eliminación permanente de todos los proyectos haciendo clic en el botón "Confirmar Eliminación Permanente" dentro del pop-up</t>
+  </si>
+  <si>
+    <t>RF0084</t>
+  </si>
+  <si>
+    <t>CREATE PROJECT</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el proceso de creación de un nuevo proyecto haciendo clic en el botón principal "+ Crear Proyecto" ubicado en el Dashboard</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0002, RNF0003, RNF0011, RNF0015, RNF0024</t>
+  </si>
+  <si>
+    <t>RF0085</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar un nombre para el nuevo proyecto haciendo clic y escribiendo en el campo de texto requerido del modal de creación de proyecto</t>
+  </si>
+  <si>
+    <t>RF0086</t>
+  </si>
+  <si>
+    <t>El usuario debe seleccionar un Método UX haciendo clic en la tarjeta de la opción deseada para completar el formulario del modal de creación de proyecto</t>
+  </si>
+  <si>
+    <t>RF0087</t>
+  </si>
+  <si>
+    <t>El usuario puede finalizar/cancelar el proceso de Creación Proyecto haciendo clic en el botón "Crear" o “Cancelar” del modal de Creación de proyecto</t>
+  </si>
+  <si>
+    <t>RF00186</t>
+  </si>
+  <si>
+    <t>Épica 3 - Orquestador y Contrato de Módulos (Factory)</t>
+  </si>
+  <si>
+    <t>Portal; Módulo de Usabilidad</t>
+  </si>
+  <si>
+    <t>Arquitectura Backend (sin pantalla)</t>
+  </si>
+  <si>
+    <t>El sistema debe instanciar dinámicamente una implementación concreta de módulo de usabilidad mediante el Factory, según el tipo de método seleccionado al crear el proyecto</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0028</t>
+  </si>
+  <si>
+    <t>RF00187</t>
+  </si>
+  <si>
+    <t>El sistema debe validar que el tipo de módulo solicitado esté registrado en el catálogo del Factory antes de crear el proyecto, rechazando la operación en caso contrario</t>
+  </si>
+  <si>
+    <t>RNF0013</t>
+  </si>
+  <si>
+    <t>RF00188</t>
+  </si>
+  <si>
+    <t>El sistema debe inicializar el módulo instanciado antes de habilitar la participación de usuarios finales en el proyecto</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0021</t>
+  </si>
+  <si>
+    <t>RF00189</t>
+  </si>
+  <si>
+    <t>Todo módulo concreto debe implementar el contrato común de módulo de usabilidad, exponiendo de forma homogénea sus operaciones de inicialización, métricas y validación de datos</t>
+  </si>
+  <si>
+    <t>RNF0028</t>
+  </si>
+  <si>
+    <t>RF00190</t>
+  </si>
+  <si>
+    <t>El sistema debe validar la estructura de los datos enviados por el participante contra el módulo correspondiente antes de persistir cualquier resultado</t>
+  </si>
+  <si>
+    <t>RNF0009, RNF0013</t>
+  </si>
+  <si>
+    <t>RF00191</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir consultar un resumen de métricas de cualquier proyecto en un formato homogéneo, sin importar el tipo de módulo utilizado</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0028</t>
+  </si>
+  <si>
+    <t>RF00192</t>
+  </si>
+  <si>
+    <t>El sistema debe controlar las transiciones de estado del ciclo de vida del proyecto (Edición → Publicado → Finalizado), restringiendo qué acciones son válidas en cada estado</t>
+  </si>
+  <si>
+    <t>RF00199</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir que cada módulo reciba y almacene sus propios parámetros de configuración de forma independiente al Portal, sin que este último conozca su estructura interna</t>
+  </si>
+  <si>
+    <t>RNF0028, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0110</t>
+  </si>
+  <si>
+    <t>Épica 4 - Entorno de Participante y Accesibilidad</t>
+  </si>
+  <si>
+    <t>Participante</t>
+  </si>
+  <si>
+    <t>ACCESSIBILITY SETTINGS</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a las opciones de usabilidad (lectores de pantalla, contraste y tamaño de fuente) haciendo clic en la pestaña (tabs) "Accesibilidad"</t>
+  </si>
+  <si>
+    <t>RNF0011, RNF0012, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0111</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar el tamaño de fuente (Pequeño/Mediano/Grande) mediante botones de opción o un deslizador en la pestaña Accesibilidad de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0112</t>
+  </si>
+  <si>
+    <t>El usuario puede activar o desactivar el modo de Alto Contraste mediante un interruptor en la pestaña Accesibilidad de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0113</t>
+  </si>
+  <si>
+    <t>El usuario puede activar o desactivar la reducción de animaciones de la interfaz mediante un interruptor en la pestaña Accesibilidad de los Ajustes</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0012, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0114</t>
+  </si>
+  <si>
+    <t>El usuario puede visualizar la lista completa de Atajos de Teclado disponibles haciendo clic en el enlace o botón "Ver Lista" en la pestaña Accesibilidad de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0115</t>
+  </si>
+  <si>
+    <t>El usuario puede aplicar, guardar o descartar las modificaciones realizadas en las preferencias de Accesibilidad a través de los botones de acción ubicados al final de la pestaña</t>
+  </si>
+  <si>
+    <t>RF0167</t>
+  </si>
+  <si>
+    <t>ATAJOS</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar a la Pantalla Principal (Dashboard) desde cualquier ubicación presionando la combinación de teclas Alt + D</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0004, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0168</t>
+  </si>
+  <si>
+    <t>El usuario puede abrir el Centro de Ayuda presionando la combinación de teclas Alt + H</t>
+  </si>
+  <si>
+    <t>RF0169</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la Pantalla de Ajustes (Perfil, Preferencias, etc.) presionando la combinación de teclas Alt +</t>
+  </si>
+  <si>
+    <t>RF0170</t>
+  </si>
+  <si>
+    <t>El usuario puede cerrar la sesión activa presionando la combinación de teclas Alt + Q</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0008, RNF0009, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0171</t>
+  </si>
+  <si>
+    <t>El usuario puede desplegar el Menú del Perfil presionando la combinación de teclas Alt + U</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0172</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la Pantalla de Papelera presionando la combinación de teclas Alt + P</t>
+  </si>
+  <si>
+    <t>RF0173</t>
+  </si>
+  <si>
+    <t>El usuario puede abrir el formulario o modal para la creación de un nuevo proyecto presionando la combinación de teclas Ctrl + N</t>
+  </si>
+  <si>
+    <t>RF0174</t>
+  </si>
+  <si>
+    <t>El usuario puede activar el foco directo en la barra de búsqueda principal presionando la tecla / (barra) o la combinación Ctrl + F</t>
+  </si>
+  <si>
+    <t>RF0175</t>
+  </si>
+  <si>
+    <t>El usuario puede alternar cíclicamente entre las diferentes vistas del Dashboard (Lista, Cuadrícula, Kanban) presionando la combinación de teclas Ctrl + L</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0176</t>
+  </si>
+  <si>
+    <t>El usuario puede moverse verticalmente entre los proyectos seleccionables de la lista o cuadrícula presionando las teclas ↑ (Flecha Arriba) o ↓ (Flecha Abajo)</t>
+  </si>
+  <si>
+    <t>RF0177</t>
+  </si>
+  <si>
+    <t>El usuario puede abrir el proyecto que se encuentra actualmente resaltado o seleccionado presionando la tecla Enter</t>
+  </si>
+  <si>
+    <t>RF0178</t>
+  </si>
+  <si>
+    <t>El usuario puede marcar o desmarcar el proyecto actualmente seleccionado o abierto como favorito presionando la tecla F</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0013, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0179</t>
+  </si>
+  <si>
+    <t>El usuario puede archivar el proyecto actualmente seleccionado o abierto presionando la tecla A</t>
+  </si>
+  <si>
+    <t>RF0180</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el proceso de eliminación del proyecto presionando la tecla Del o la combinación Ctrl + Supr</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0010, RNF0013, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0181</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar hacia el siguiente elemento interactivo de la interfaz (botones, enlaces, campos de formulario) presionando la tecla Tab</t>
+  </si>
+  <si>
+    <t>RF0182</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar hacia el elemento interactivo anterior de la interfaz (botones, enlaces, campos de formulario) presionando la combinación de teclas Shift + Tab</t>
+  </si>
+  <si>
+    <t>RF0183</t>
+  </si>
+  <si>
+    <t>El usuario puede ejecutar la acción del botón, enlace o campo actualmente enfocado presionando la tecla Enter</t>
+  </si>
+  <si>
+    <t>RF0184</t>
+  </si>
+  <si>
+    <t>El usuario puede cerrar cualquier modal, diálogo, tooltip o menú abierto presionando la tecla Esc (Escape)</t>
+  </si>
+  <si>
+    <t>RF0185</t>
+  </si>
+  <si>
+    <t>El usuario puede activar el texto descriptivo adicional o tooltip de un elemento actualmente enfocado presionando la combinación de teclas Alt + I</t>
+  </si>
+  <si>
+    <t>RF00193</t>
+  </si>
+  <si>
+    <t>Épica 5 - Motor de Telemetría</t>
+  </si>
+  <si>
+    <t>Motor de Telemetría; Participante; Investigador</t>
+  </si>
+  <si>
+    <t>El sistema debe establecer y mantener una conexión WebSocket activa entre el cliente participante y el servidor durante toda la sesión de evaluación</t>
+  </si>
+  <si>
+    <t>RNF0009, RNF0024</t>
+  </si>
+  <si>
+    <t>RF00194</t>
+  </si>
+  <si>
+    <t>El sistema debe registrar cada conexión entrante y liberar los recursos asociados automáticamente cuando la sesión finaliza o se pierde la conexión</t>
+  </si>
+  <si>
+    <t>RNF0021, RNF0024</t>
+  </si>
+  <si>
+    <t>RF00195</t>
+  </si>
+  <si>
+    <t>El sistema debe capturar los eventos de interacción del participante (foco, posición en el DOM, timestamp) durante la ejecución de la tarea</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0009</t>
+  </si>
+  <si>
+    <t>RF00196</t>
+  </si>
+  <si>
+    <t>El sistema debe procesar cada evento de telemetría recibido y persistirlo junto con sus metadatos en formato JSONB</t>
+  </si>
+  <si>
+    <t>RNF0009, RNF0025</t>
+  </si>
+  <si>
+    <t>RF00197</t>
+  </si>
+  <si>
+    <t>El sistema debe transmitir en tiempo real los eventos relevantes de la sesión hacia el panel del investigador conectado</t>
+  </si>
+  <si>
+    <t>RF00198</t>
+  </si>
+  <si>
+    <t>El sistema debe asociar cada evento de telemetría a su identificador de sesión y marca de tiempo, permitiendo reconstruir cronológicamente la sesión completa</t>
+  </si>
+  <si>
+    <t>RNF0025, RNF0022</t>
+  </si>
+  <si>
+    <t>RF0059</t>
+  </si>
+  <si>
+    <t>Épica 8 - Monetización y Suscripciones</t>
+  </si>
+  <si>
+    <t>Congelada</t>
+  </si>
+  <si>
+    <t>Investigador</t>
+  </si>
+  <si>
+    <t>PREMIUM SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el flujo de actualización de la cuenta haciendo clic en el botón "FREE" ubicado en el Header del Dashboard</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0003, RNF0011, RNF0024, RNF0027</t>
+  </si>
+  <si>
+    <t>Won't have</t>
+  </si>
+  <si>
+    <t>RF0060</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar el plan que quiera al dar click en el botón FREE ubicado en el Header de la página (Etapa 1)</t>
+  </si>
+  <si>
+    <t>RF0061</t>
+  </si>
+  <si>
+    <t>El usuario puede confirmar su intención de compra haciendo clic en el botón "Continuar con el Pago" en la Pantalla de Pago (Etapa 1)</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0009, RNF0011, RNF0013, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0062</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla Principal haciendo clic en el botón “Cancelar” durante el flujo de pago suscripción en la Pantalla de Pago (Etapa 1)</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0004, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0063</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar el método de pago (ej. Tarjeta de Crédito/Débito, PayPal) mediante botones de opciones en la Pantalla de Pago (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RF0064</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar el Número de la Tarjeta en el campo de texto provisto en la Pantalla de Pago (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RNF0006, RNF0009, RNF0011, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0065</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar el Nombre Completo tal como aparece en la tarjeta en el campo correspondiente en la Pantalla de Pago (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RNF0009, RNF0011, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0066</t>
+  </si>
+  <si>
+    <t>El usuario debe seleccionar la Fecha de Vencimiento (Mes y Año) de la tarjeta usando menús desplegables en la Pantalla de Pago (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RF0067</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar el Código de Seguridad (CVV) en el campo de texto provisto en la Pantalla de Pago (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RF0068</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar la dirección de facturación (Calle, Ciudad, Código Postal, País) en los campos de texto y listas desplegables obligatorios en la Pantalla de Pago (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RF0069</t>
+  </si>
+  <si>
+    <t>El usuario puede ejecutar el pago y la suscripción haciendo clic en el botón "Pagar y Suscribirse" o dar click en el botón Regresar (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0006, RNF0009, RNF0010, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0070</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar el ciclo de facturación (ej. Mensual / Anual), lo que actualiza el precio final mostrado en la Pantalla de Pago (Etapa 2)</t>
+  </si>
+  <si>
+    <t>RF0071</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Confirmación de Suscripción después de que la pasarela de pago confirma que la transacción fue exitosa en la Pantalla de Pago (Etapa 3)</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0004, RNF0011, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0072</t>
+  </si>
+  <si>
+    <t>El usuario puede regresar a la Pantalla Principal haciendo clic en el botón principal "Ir al Dashboard" al finalizar la transacción en la Pantalla de Pago (Etapa 3)</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0004, RNF0011, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0073</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la pestaña de gestión de su suscripción haciendo clic en un enlace secundario como "Gestionar Facturación", que lo lleva directamente a la pestaña "Suscripción / Facturación" desde la Pantalla de Pago (Etapa 3)</t>
+  </si>
+  <si>
+    <t>RF0128</t>
+  </si>
+  <si>
+    <t>PREMIUM SETTINGS</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la gestión de su plan, pagos y facturación haciendo clic en la pestaña (tab) "Suscripción / Facturación"</t>
+  </si>
+  <si>
+    <t>RF0129</t>
+  </si>
+  <si>
+    <t>El usuario puede cambiar el método de pago (ej. actualizar tarjeta) abriendo el formulario de pago simplificado en la pestaña Suscripción / Facturación de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0130</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder y descargar el historial de facturación (recibos) en un formato legible en la pestaña Suscripción / Facturación de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0131</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el flujo de Cancelación de Suscripción haciendo clic en el botón "Cancelar Suscripción" en la pestaña Suscripción / Facturación de los Ajustes</t>
+  </si>
+  <si>
+    <t>RF0132</t>
+  </si>
+  <si>
+    <t>El usuario puede confirmar la cancelación definitiva haciendo clic en el botón destructivo "Cancelar Suscripción de Todos Modos"</t>
+  </si>
+  <si>
+    <t>RF0133</t>
+  </si>
+  <si>
+    <t>El usuario puede cancelar el proceso de Cancelación de Suscripción y volver a la pestaña de gestión haciendo clic en el botón "Regresar"</t>
+  </si>
+  <si>
+    <t>RF0134</t>
+  </si>
+  <si>
+    <t>El usuario puede cambiar el ciclo de facturación (ej. de Mensual a Anual) o cambiar el plan haciendo clic en el botón "Cambiar Plan/Ciclo"</t>
+  </si>
+  <si>
+    <t>RF0135</t>
+  </si>
+  <si>
+    <t>Épica 9 - Soporte, Ayuda y Onboarding</t>
+  </si>
+  <si>
+    <t>HELP SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar a la Página Principal del Centro de Ayuda haciendo clic en el logo “MEUX Lab | Centro de Ayuda”</t>
+  </si>
+  <si>
+    <t>RNF0001, RNF0011</t>
+  </si>
+  <si>
+    <t>RF0136</t>
+  </si>
+  <si>
+    <t>El usuario puede cambiar el idioma de la interfaz de la plataforma haciendo clic en el menú desplegable de Idiomas ubicado en el Header del Centro de Ayuda</t>
+  </si>
+  <si>
+    <t>RF0137</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Reporte haciendo clic en el botón "Contáctenos" ubicado en el Header del Centro de Ayuda</t>
+  </si>
+  <si>
+    <t>RF0138</t>
+  </si>
+  <si>
+    <t>MAIN HELP SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede buscar artículos de apoyo, guías y tutoriales escribiendo en la barra de búsqueda principal de la Pantalla Principal del Centro de Ayuda</t>
+  </si>
+  <si>
+    <t>RF0139</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar a la Página de Listado de Subtemas de una categoría principal haciendo clic en la Tarjeta de Tema correspondiente</t>
+  </si>
+  <si>
+    <t>RF0140</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder al contenido detallado de un artículo haciendo clic en el título de un Subtema de la lista</t>
+  </si>
+  <si>
+    <t>RF0141</t>
+  </si>
+  <si>
+    <t>El usuario puede saltar a secciones específicas dentro del artículo haciendo clic en los enlaces de la Tabla de Contenidos en el Artículo</t>
+  </si>
+  <si>
+    <t>RF0142</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar a la fuente externa o al recurso vinculado haciendo clic en los enlaces de hipertexto incluidos en el cuerpo del Artículo</t>
+  </si>
+  <si>
+    <t>RNF0004, RNF0011, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0143</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar hacia atrás a cualquier nivel jerárquico superior haciendo clic en cualquiera de los enlaces de la Ruta de Navegación ubicada en la parte superior del Artículo</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0004, RNF0011, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0144</t>
+  </si>
+  <si>
+    <t>HELP SIDEBAR MENU</t>
+  </si>
+  <si>
+    <t>El usuario puede expandir y colapsar la lista de Subtemas en la Pantalla Principal del Centro de Ayuda haciendo clic en el título de la Categoría Principal (Tema) en el Menú Lateral</t>
+  </si>
+  <si>
+    <t>RF0145</t>
+  </si>
+  <si>
+    <t>El usuario puede navegar y visualizar el contenido completo de cualquier Subtema/Artículo de la Pantalla Principal del Centro de Ayuda haciendo clic en el título del elemento expandido</t>
+  </si>
+  <si>
+    <t>RF0146</t>
+  </si>
+  <si>
+    <t>El usuario puede volver a la parte superior de la página haciendo clic en el ícono de flecha arriba que es visible cuando se encuentra en la parte inferior de un artículo largo</t>
+  </si>
+  <si>
+    <t>RF0147</t>
+  </si>
+  <si>
+    <t>USER HELP SCREEN MENU</t>
+  </si>
+  <si>
+    <t>El usuario puede desplegar el Menú de Administración del Perfil haciendo clic en su Foto de Perfil ubicada en el Header del Centro de Ayuda</t>
+  </si>
+  <si>
+    <t>RF0148</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Pantalla de Seguimiento de Soporte haciendo clic en la opción "Mi Actividad" en el Menú de Administración del Perfil</t>
+  </si>
+  <si>
+    <t>RF0149</t>
+  </si>
+  <si>
+    <t>El usuario es redirigido a la Landing Page y su sesión se cierra haciendo clic en la opción "Cerrar Sesión" en el Menú de Administración del Perfil</t>
+  </si>
+  <si>
+    <t>RF0150</t>
+  </si>
+  <si>
+    <t>REPORT SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar la clasificación de la solicitud (ej. Reporte de Error, Solicitud de Función, Consulta General) antes de llenar el formulario principal de la Pantalla de Reporte</t>
+  </si>
+  <si>
+    <t>RF0151</t>
+  </si>
+  <si>
+    <t>El usuario debe ingresar un Asunto conciso y una Descripción detallada de la solicitud en los campos de texto correspondientes</t>
+  </si>
+  <si>
+    <t>RF0152</t>
+  </si>
+  <si>
+    <t>El usuario puede finalizar y enviar la solicitud al equipo de soporte haciendo clic en el botón "Enviar Solicitud"</t>
+  </si>
+  <si>
+    <t>RF0153</t>
+  </si>
+  <si>
+    <t>ACTIVITY SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede filtrar el listado de solicitudes de soporte haciendo clic en las pestañas (tabs) de estado: "Enviado", "En Revisión" y "Contestado"</t>
+  </si>
+  <si>
+    <t>RF0154</t>
+  </si>
+  <si>
+    <t>El usuario puede acceder a la vista detallada de la descripción del ticket haciendo clic en la tarjeta o fila de una solicitud en el listado</t>
+  </si>
+  <si>
+    <t>RF0155</t>
+  </si>
+  <si>
+    <t>El usuario puede alternar el ordenamiento del listado (Ascendente/Descendente) haciendo clic en el icono de flechas de ordenamiento ubicado en el encabezado de la columna de fecha</t>
+  </si>
+  <si>
+    <t>RF0156</t>
+  </si>
+  <si>
+    <t>FEEDBACK</t>
+  </si>
+  <si>
+    <t>El usuario puede cerrar el Formulario de Feedback emergente haciendo clic en el ícono de "Cerrar" (X) en la ventana del Artículo</t>
+  </si>
+  <si>
+    <t>RF0157</t>
+  </si>
+  <si>
+    <t>El usuario puede enviar retroalimentación positiva haciendo clic en el botón "Sí" en el Formulario de feedback emergente en la ventana del Artículo</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0009, RNF0013</t>
+  </si>
+  <si>
+    <t>RF0158</t>
+  </si>
+  <si>
+    <t>El usuario puede iniciar el flujo de detalle haciendo clic en el botón "No" en el Formulario de feedback emergente en la ventana del Artículo</t>
+  </si>
+  <si>
+    <t>RF0159</t>
+  </si>
+  <si>
+    <t>El usuario puede seleccionar opciones de clasificación haciendo clic en las opciones disponibles en el Formulario de feedback emergente en la ventana del Artículo</t>
+  </si>
+  <si>
+    <t>RNF0003, RNF0011, RNF0013, RNF0014, RNF0015</t>
+  </si>
+  <si>
+    <t>RF0160</t>
+  </si>
+  <si>
+    <t>El usuario puede proporcionar comentarios detallados escribiendo en el campo de texto en el Formulario de feedback emergente en la ventana del Artículo</t>
+  </si>
+  <si>
+    <t>RNF0011, RNF0013, RNF0014</t>
+  </si>
+  <si>
+    <t>RF0161</t>
+  </si>
+  <si>
+    <t>El usuario puede enviar la retroalimentación negativa final haciendo clic en el botón "Enviar" en el Formulario de feedback emergente en la ventana del Artículo</t>
+  </si>
+  <si>
+    <t>RF0162</t>
+  </si>
+  <si>
+    <t>El usuario puede retroceder en el formulario haciendo clic en el ícono de "Flecha Atrás" en el Formulario de feedback emergente en la ventana del Artículo</t>
+  </si>
+  <si>
+    <t>RF0163</t>
+  </si>
+  <si>
+    <t>TUTORIAL SCREEN</t>
+  </si>
+  <si>
+    <t>El usuario puede decidir iniciar u omitir la Guía Interactiva después de registrarse desde la Pantalla de Bienvenida</t>
+  </si>
+  <si>
+    <t>RF0164</t>
+  </si>
+  <si>
+    <t>El usuario puede avanzar al siguiente paso de la Guía Interactiva haciendo clic en el botón "Siguiente" en el tooltip del paso actual</t>
+  </si>
+  <si>
+    <t>RF0165</t>
+  </si>
+  <si>
+    <t>El usuario puede retroceder al paso anterior haciendo clic en el botón "Anterior" en el tooltip de la Guía Interactiva (disponible a partir del Paso 2)</t>
+  </si>
+  <si>
+    <t>RF0166</t>
+  </si>
+  <si>
+    <t>El usuario puede finalizar el la Guía Interactiva haciendo clic en el botón "Finalizar Recorrido" y comenzar a usar la aplicación</t>
+  </si>
+  <si>
+    <t>RNF0002, RNF0011, RNF0013, RNF0015</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Total RF</t>
+  </si>
+  <si>
+    <t>Alta Prioridad</t>
+  </si>
+  <si>
+    <t>Moderada Prioridad</t>
+  </si>
+  <si>
+    <t>Baja Prioridad</t>
+  </si>
+  <si>
+    <t>Distribución MoSCoW (Backlog Completo)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Épica 6 - Módulos Específicos</t>
+  </si>
+  <si>
+    <t>Épica 7 - Métricas, Reportes e Inteligencia de Datos</t>
+  </si>
+  <si>
+    <t>ID RNF</t>
+  </si>
+  <si>
+    <t>Nombre / Resumen</t>
+  </si>
+  <si>
+    <t># RF Asociados</t>
+  </si>
+  <si>
+    <t>RF que lo referencian</t>
+  </si>
+  <si>
+    <t>RNF0001</t>
+  </si>
+  <si>
+    <t>La carga inicial completa (renderización y listado de datos) de las vistas principales (Dashboard, Ajustes, Proyectos) debe ser completada en: Menos de 3 segundos para el 90% de las solicitudes</t>
+  </si>
+  <si>
+    <t>RF0120, RF0121, RF0122, RF0126, RF0127, RF0020, RF0021, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0052, RF0056, RF0058, RF0077, RF0082, RF0083, RF0084, RF0086, RF00191, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0135, RF0136, RF0137, RF0138, RF0139, RF0140, RF0145, RF0146, RF0147, RF0148, RF0149, RF0152, RF0153</t>
+  </si>
+  <si>
+    <t>RNF0002</t>
+  </si>
+  <si>
+    <t>El tiempo de procesamiento de todas las transacciones de escritura (Registro, Login, Creación de Proyecto, Confirmación de Eliminación) debe ser retornado al usuario en: Menos de 2 segundos desde la interacción</t>
+  </si>
+  <si>
+    <t>RF0008, RF0012, RF0013, RF0016, RF0017, RF0096, RF0101, RF0108, RF0123, RF0124, RF0125, RF0036, RF0078, RF0079, RF0080, RF0081, RF0084, RF0087, RF00186, RF00188, RF0115, RF0170, RF0178, RF0179, RF0180, RF0059, RF0069, RF0071, RF0144, RF0150, RF0151, RF0154, RF0155, RF0157, RF0161, RF0166</t>
+  </si>
+  <si>
+    <t>RNF0003</t>
+  </si>
+  <si>
+    <t>Los elementos dinámicos de la interfaz (despliegue de Modales, Menús Contextuales, Tooltips o Pop-ups de confirmación) deben ser mostrados y responder a las interacciones del usuario en: Menos de 200 milisegundos</t>
+  </si>
+  <si>
+    <t>RF0014, RF0088, RF0089, RF0090, RF0091, RF0092, RF0093, RF0094, RF0095, RF0096, RF0097, RF0098, RF0099, RF0100, RF0101, RF0102, RF0103, RF0104, RF0105, RF0106, RF0107, RF0108, RF0109, RF0116, RF0117, RF0118, RF00119, RF0120, RF0121, RF0122, RF0123, RF0124, RF0125, RF0126, RF0127, RF0019, RF0020, RF0021, RF0022, RF0023, RF0024, RF0025, RF0026, RF0027, RF0028, RF0029, RF0030, RF0031, RF0032, RF0033, RF0034, RF0035, RF0037, RF0038, RF0039, RF0040, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0049, RF0050, RF0051, RF0052, RF0053, RF0054, RF0055, RF0056, RF0057, RF0058, RF0074, RF0075, RF0076, RF0077, RF0078, RF0079, RF0080, RF0081, RF0082, RF0083, RF0084, RF0085, RF0086, RF0087, RF0113, RF0115, RF0167, RF0168, RF0169, RF0171, RF0172, RF0173, RF0174, RF0175, RF0176, RF0177, RF0181, RF0182, RF0183, RF0184, RF0185, RF00195, RF00197, RF0059, RF0060, RF0061, RF0062, RF0063, RF0070, RF0072, RF0073, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0136, RF0137, RF0138, RF0139, RF0140, RF0141, RF0143, RF0144, RF0145, RF0146, RF0147, RF0148, RF0149, RF0150, RF0151, RF0152, RF0153, RF0154, RF0155, RF0156, RF0158, RF0159, RF0162, RF0163, RF0164, RF0165</t>
+  </si>
+  <si>
+    <t>RNF0004</t>
+  </si>
+  <si>
+    <t>El tiempo transcurrido desde que se hace clic en un enlace de navegación hasta que la nueva página comienza a cargarse debe ser de: Menos de 1 segundo</t>
+  </si>
+  <si>
+    <t>RF0002, RF0003, RF0004, RF0005, RF0006, RF0007, RF0015, RF0018, RF0167, RF0168, RF0169, RF0172, RF0177, RF0062, RF0071, RF0072, RF0073, RF0142, RF0143</t>
+  </si>
+  <si>
+    <t>RNF0005</t>
+  </si>
+  <si>
+    <t>Las solicitudes a procesos secundarios (ej. reenvío de correos, generación de reportes ligeros) deben ser procesadas y el feedback mostrado al usuario en: Menos de 5 segundos</t>
+  </si>
+  <si>
+    <t>RNF0006</t>
+  </si>
+  <si>
+    <t>Todas las contraseñas de usuario deben ser almacenadas y procesadas utilizando métodos criptográficos seguros: Utilizar un algoritmo de hashing unidireccional (ej. bcrypt o Argon2) con un factor de salting único y aleatorio</t>
+  </si>
+  <si>
+    <t>RF0008, RF0012, RF0013, RF0017, RF0064, RF0067, RF0069</t>
+  </si>
+  <si>
+    <t>RNF0007</t>
+  </si>
+  <si>
+    <t>El sistema debe monitorear y restringir los intentos fallidos de inicio de sesión: Bloquear temporalmente la cuenta o la dirección IP por 30 minutos después de 5 intentos fallidos de contraseña</t>
+  </si>
+  <si>
+    <t>RNF0008</t>
+  </si>
+  <si>
+    <t>El sistema debe invalidar inmediatamente todas las sesiones activas, excepto la actual, al confirmarse la acción de "Cerrar Sesión en Todos los Dispositivos": Invalidación en tiempo real de los tokens de sesión remota al ejecutar el RF de cierre de sesión remota</t>
+  </si>
+  <si>
+    <t>RF0036, RF0170</t>
+  </si>
+  <si>
+    <t>RNF0009</t>
+  </si>
+  <si>
+    <t>Toda la comunicación de datos entre el navegador del usuario y el servidor (incluyendo login, formularios y solicitudes a API) debe ser cifrada: Utilizar el protocolo HTTPS/TLS 1.2 o superior de extremo a extremo</t>
+  </si>
+  <si>
+    <t>RF0008, RF0011, RF0012, RF0013, RF0017, RF0036, RF0075, RF00190, RF0170, RF00193, RF00195, RF00196, RF00197, RF0061, RF0063, RF0064, RF0065, RF0066, RF0067, RF0068, RF0069, RF0157, RF0161</t>
+  </si>
+  <si>
+    <t>RNF0010</t>
+  </si>
+  <si>
+    <t>Al confirmar la "Eliminación Permanente de Cuenta" o "Eliminación Definitiva de Proyectos", los datos asociados deben ser marcados para borrado y retirados del almacenamiento: Eliminación lógica e irreversible de todos los datos personales y de proyecto en un plazo máximo de 72 horas</t>
+  </si>
+  <si>
+    <t>RF0075, RF0180, RF0069</t>
+  </si>
+  <si>
+    <t>RNF0011</t>
+  </si>
+  <si>
+    <t>Todos los elementos de la interfaz (header, footer, botones, formularios, paleta de colores y tipografía) deben ser uniformes y coherentes en todas las vistas, desde la Landing Page hasta las pantallas internas de la aplicación. Cumplir al 100% con la guía de estilo y el branding definidos en el Design System</t>
+  </si>
+  <si>
+    <t>RF0001, RF0002, RF0003, RF0004, RF0005, RF0006, RF0007, RF0008, RF0009, RF0010, RF0011, RF0014, RF0015, RF0088, RF0089, RF0090, RF0091, RF0092, RF0093, RF0094, RF0095, RF0096, RF0097, RF0098, RF0099, RF0100, RF0101, RF0102, RF0103, RF0104, RF0105, RF0106, RF0107, RF0108, RF0109, RF0116, RF0117, RF0118, RF00119, RF0120, RF0121, RF0122, RF0123, RF0124, RF0125, RF0126, RF0127, RF0018, RF0019, RF0020, RF0021, RF0022, RF0023, RF0024, RF0025, RF0026, RF0027, RF0028, RF0029, RF0030, RF0031, RF0032, RF0033, RF0034, RF0035, RF0036, RF0037, RF0038, RF0039, RF0040, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0049, RF0050, RF0051, RF0052, RF0053, RF0054, RF0055, RF0056, RF0057, RF0058, RF0074, RF0075, RF0076, RF0077, RF0078, RF0079, RF0080, RF0081, RF0082, RF0083, RF0084, RF0085, RF0086, RF0087, RF0110, RF0111, RF0112, RF0113, RF0114, RF0115, RF0175, RF0176, RF0185, RF0059, RF0060, RF0061, RF0063, RF0064, RF0065, RF0066, RF0067, RF0068, RF0070, RF0071, RF0072, RF0073, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0135, RF0136, RF0137, RF0138, RF0139, RF0140, RF0141, RF0142, RF0143, RF0144, RF0145, RF0146, RF0147, RF0148, RF0149, RF0150, RF0151, RF0152, RF0153, RF0154, RF0155, RF0158, RF0159, RF0160, RF0163, RF0164, RF0165, RF0166</t>
+  </si>
+  <si>
+    <t>RNF0012</t>
+  </si>
+  <si>
+    <t>El diseño de la aplicación debe ajustarse dinámicamente para mantener la funcionalidad, legibilidad y estética: Funcionalidad y usabilidad completas en resoluciones desde 320px (móvil) hasta 1920px (escritorio), sin necesidad de scroll horizontal</t>
+  </si>
+  <si>
+    <t>RF0001, RF0002, RF0003, RF0004, RF0005, RF0006, RF0007, RF0088, RF0089, RF0095, RF0097, RF0098, RF0099, RF0100, RF0102, RF0103, RF0104, RF0105, RF0106, RF0107, RF0116, RF0117, RF0118, RF00119, RF0018, RF0019, RF0031, RF0032, RF0033, RF0034, RF0035, RF0037, RF0038, RF0039, RF0040, RF0041, RF0057, RF0058, RF0110, RF0111, RF0112, RF0113, RF0114</t>
+  </si>
+  <si>
+    <t>El sistema debe proporcionar feedback visual y textual inmediato al usuario tras cualquier interacción (positiva, negativa o neutra): Mostrar mensajes de confirmación de éxito (ej. "Contraseña Actualizada"), advertencias, y mensajes de error claros y accionables (código y descripción)</t>
+  </si>
+  <si>
+    <t>RF0014, RF0015, RF0016, RF0090, RF0091, RF0092, RF0093, RF0094, RF0096, RF0101, RF0108, RF0109, RF0120, RF0121, RF0122, RF0123, RF0124, RF0125, RF0126, RF0127, RF0020, RF0024, RF0025, RF0026, RF0028, RF0029, RF0030, RF0047, RF0048, RF0052, RF0055, RF0056, RF0074, RF0075, RF0076, RF0077, RF0078, RF0079, RF0080, RF0081, RF0082, RF0083, RF0085, RF0087, RF00187, RF00190, RF00192, RF00199, RF0115, RF0178, RF0179, RF0180, RF0060, RF0061, RF0063, RF0064, RF0065, RF0066, RF0067, RF0068, RF0069, RF0071, RF0128, RF0129, RF0130, RF0131, RF0132, RF0133, RF0134, RF0136, RF0137, RF0138, RF0139, RF0140, RF0144, RF0145, RF0146, RF0147, RF0148, RF0149, RF0150, RF0151, RF0152, RF0153, RF0154, RF0155, RF0157, RF0158, RF0159, RF0160, RF0161, RF0163, RF0164, RF0166</t>
+  </si>
+  <si>
+    <t>RNF0014</t>
+  </si>
+  <si>
+    <t>La funcionalidad clave de la aplicación debe ser accesible y operable sin el uso del mouse, incluyendo la navegación entre elementos, la activación de botones y el cierre de modales: Cumplir con el estándar WCAG 2.1 Nivel A y garantizar la operación completa mediante las teclas Tab, Shift+Tab y Esc</t>
+  </si>
+  <si>
+    <t>RF0110, RF0111, RF0112, RF0113, RF0114, RF0167, RF0168, RF0169, RF0170, RF0171, RF0172, RF0173, RF0174, RF0175, RF0176, RF0177, RF0178, RF0179, RF0180, RF0181, RF0182, RF0183, RF0184, RF0185, RF0141, RF0143, RF0156, RF0159, RF0160, RF0162, RF0164, RF0165</t>
+  </si>
+  <si>
+    <t>RNF0015</t>
+  </si>
+  <si>
+    <t>Todos los patrones de interacción definidos (ej. arrastrar y soltar, tooltips, modales de confirmación) deben comportarse de forma predecible y consistente a lo largo de toda la aplicación. El uso de la tecla Esc debe cerrar cualquier ventana emergente, menú contextual o tooltip activo</t>
+  </si>
+  <si>
+    <t>RF0001, RF0014, RF0088, RF0089, RF0090, RF0091, RF0092, RF0093, RF0094, RF0100, RF0109, RF0122, RF0125, RF0019, RF0022, RF0023, RF0024, RF0025, RF0027, RF0029, RF0041, RF0042, RF0043, RF0044, RF0045, RF0046, RF0047, RF0048, RF0049, RF0050, RF0052, RF0053, RF0054, RF0055, RF0056, RF0057, RF0058, RF0074, RF0075, RF0076, RF0078, RF0079, RF0084, RF0085, RF0086, RF0087, RF0110, RF0111, RF0112, RF0113, RF0114, RF0167, RF0168, RF0169, RF0170, RF0171, RF0172, RF0173, RF0174, RF0175, RF0176, RF0177, RF0178, RF0179, RF0180, RF0181, RF0182, RF0183, RF0184, RF0185, RF0060, RF0061, RF0062, RF0063, RF0070, RF0072, RF0073, RF0131, RF0133, RF0136, RF0138, RF0141, RF0142, RF0143, RF0149, RF0154, RF0155, RF0156, RF0158, RF0159, RF0162, RF0163, RF0164, RF0165, RF0166</t>
+  </si>
+  <si>
+    <t>RNF0016</t>
+  </si>
+  <si>
+    <t>La aplicación debe garantizar funcionalidad completa y rendimiento óptimo en los navegadores más utilizados: Soporte total para las dos últimas versiones estables de Google Chrome, Mozilla Firefox, Apple Safari y Microsoft Edge</t>
+  </si>
+  <si>
+    <t>RNF0017</t>
+  </si>
+  <si>
+    <t>La interfaz debe mantener la coherencia visual y la funcionalidad en diferentes plataformas de escritorio y móviles: Soporte total para las dos últimas versiones principales de Windows, macOS, Android (Chrome) e iOS (Safari)</t>
+  </si>
+  <si>
+    <t>RNF0018</t>
+  </si>
+  <si>
+    <t>La aplicación debe adherirse a los estándares web actuales para garantizar la interoperabilidad y el rendimiento a largo plazo: Todo el código front-end debe ser válido según los estándares HTML5, CSS3 y JavaScript ES6 o superior</t>
+  </si>
+  <si>
+    <t>RF0089, RF0095</t>
+  </si>
+  <si>
+    <t>RNF0019</t>
+  </si>
+  <si>
+    <t>La aplicación debe ser completamente funcional y legible incluso en las resoluciones de pantalla más pequeñas utilizadas por el mercado objetivo: Soporte completo para una resolución mínima de 360px de ancho en dispositivos móviles y 1280x720 en escritorio</t>
+  </si>
+  <si>
+    <t>RF0055, RF0074</t>
+  </si>
+  <si>
+    <t>RNF0020</t>
+  </si>
+  <si>
+    <t>El sistema debe estar accesible y completamente funcional para los usuarios finales: Garantizar una disponibilidad (uptime) mínima del 99.9% durante el horario de servicio (24/7)</t>
+  </si>
+  <si>
+    <t>RNF0021</t>
+  </si>
+  <si>
+    <t>En caso de fallo de un componente no crítico (ej. microservicio secundario), el sistema debe mantener la funcionalidad clave (login, creación y edición de proyectos): Mantener la operación de las funciones críticas sin degradación de rendimiento</t>
+  </si>
+  <si>
+    <t>RF0042, RF00188, RF00194</t>
+  </si>
+  <si>
+    <t>RNF0022</t>
+  </si>
+  <si>
+    <t>Se debe realizar una copia de seguridad completa de la base de datos de forma periódica: Realizar un backup completo diariamente y almacenarlo fuera del sitio por un mínimo de 7 días</t>
+  </si>
+  <si>
+    <t>RNF0023</t>
+  </si>
+  <si>
+    <t>En caso de un fallo catastrófico (ej. caída completa del servidor principal), el sistema debe ser capaz de restaurar la operación: El tiempo de recuperación total (RTO) no debe exceder las 4 horas desde la detección del fallo</t>
+  </si>
+  <si>
+    <t>— SIN COBERTURA —</t>
+  </si>
+  <si>
+    <t>RNF0024</t>
+  </si>
+  <si>
+    <t>El sistema debe mantener los umbrales de rendimiento definidos (carga &lt;3s, transacción &lt;2s) al operar simultáneamente: Soportar eficientemente 500 usuarios concurrentes activos en la plataforma</t>
+  </si>
+  <si>
+    <t>RF0084, RF00193, RF00194, RF0059</t>
+  </si>
+  <si>
+    <t>RNF0025</t>
+  </si>
+  <si>
+    <t>La arquitectura de la base de datos debe ser capaz de gestionar un volumen creciente de datos de proyecto sin degradación del rendimiento: Soportar un crecimiento de datos del 30% anual manteniendo los tiempos de respuesta definidos</t>
+  </si>
+  <si>
+    <t>RF00196, RF00198</t>
+  </si>
+  <si>
+    <t>RNF0026</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir a cada usuario individual crear y gestionar un número considerable de proyectos: Permitir la creación y gestión de 100 proyectos activos por usuario sin experimentar degradación en la carga del Dashboard</t>
+  </si>
+  <si>
+    <t>PENDIENTE — depende del modelo de suscripción (Épica 8, congelada). No es un olvido: se resolverá cuando se desarrolle Épica 8.</t>
+  </si>
+  <si>
+    <t>RNF0027</t>
+  </si>
+  <si>
+    <t>La infraestructura de hosting debe estar dimensionada para manejar picos de tráfico inducidos por campañas o lanzamientos: Soportar el doble del tráfico promedio diario durante períodos sostenidos de hasta 6 horas</t>
+  </si>
+  <si>
+    <t>Todo el código desarrollado debe seguir un estándar de codificación consistente y ser documentado con comentarios y guías para facilitar su mantenimiento</t>
+  </si>
+  <si>
+    <t>RF00186, RF00189, RF00191, RF00199</t>
+  </si>
+  <si>
+    <t>RNF0029</t>
+  </si>
+  <si>
+    <t>El sistema debe incluir enlaces visibles y accesibles a la Política de Privacidad y los Términos y Condiciones, los cuales deben ser aceptados durante el flujo de registro</t>
+  </si>
+  <si>
+    <t>RF0008, RF0009, RF0010, RF0011</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1904,46 +1917,27 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1992,14 +1986,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -2015,166 +2009,53 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF185FA5"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDDEBF7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2233,55 +2114,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2289,12 +2178,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2323,7 +2212,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2344,7 +2233,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2395,7 +2284,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2413,38 +2302,37 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M200"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="55" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2485,7 +2373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -2526,7 +2414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -2567,7 +2455,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -2608,7 +2496,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -2649,7 +2537,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -2690,7 +2578,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -2731,7 +2619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2772,7 +2660,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -2813,7 +2701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
@@ -2835,7 +2723,9 @@
       <c r="G10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="I10" s="2" t="s">
         <v>34</v>
       </c>
@@ -2852,7 +2742,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -2874,7 +2764,9 @@
       <c r="G11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="I11" s="2" t="s">
         <v>34</v>
       </c>
@@ -2891,7 +2783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>51</v>
       </c>
@@ -2913,7 +2805,9 @@
       <c r="G12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="I12" s="2" t="s">
         <v>28</v>
       </c>
@@ -2930,7 +2824,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
@@ -2971,7 +2865,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>58</v>
       </c>
@@ -3012,7 +2906,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>61</v>
       </c>
@@ -3053,7 +2947,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
@@ -3094,7 +2988,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>67</v>
       </c>
@@ -3135,7 +3029,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>71</v>
       </c>
@@ -3176,7 +3070,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>73</v>
       </c>
@@ -3217,7 +3111,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>77</v>
       </c>
@@ -3258,7 +3152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>80</v>
       </c>
@@ -3299,7 +3193,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>82</v>
       </c>
@@ -3340,7 +3234,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
@@ -3381,7 +3275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>86</v>
       </c>
@@ -3422,7 +3316,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>88</v>
       </c>
@@ -3463,7 +3357,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>90</v>
       </c>
@@ -3504,7 +3398,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>93</v>
       </c>
@@ -3545,7 +3439,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>96</v>
       </c>
@@ -3586,7 +3480,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>100</v>
       </c>
@@ -3627,7 +3521,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>102</v>
       </c>
@@ -3668,7 +3562,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>104</v>
       </c>
@@ -3709,7 +3603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>106</v>
       </c>
@@ -3750,7 +3644,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>108</v>
       </c>
@@ -3791,7 +3685,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>111</v>
       </c>
@@ -3832,7 +3726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>113</v>
       </c>
@@ -3873,7 +3767,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
@@ -3914,7 +3808,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>117</v>
       </c>
@@ -3955,7 +3849,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>119</v>
       </c>
@@ -3996,7 +3890,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>121</v>
       </c>
@@ -4037,7 +3931,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>123</v>
       </c>
@@ -4078,7 +3972,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>125</v>
       </c>
@@ -4119,7 +4013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>128</v>
       </c>
@@ -4160,7 +4054,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -4201,7 +4095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>132</v>
       </c>
@@ -4242,7 +4136,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>134</v>
       </c>
@@ -4283,7 +4177,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>137</v>
       </c>
@@ -4324,7 +4218,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>139</v>
       </c>
@@ -4365,7 +4259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>142</v>
       </c>
@@ -4406,7 +4300,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>144</v>
       </c>
@@ -4447,7 +4341,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>146</v>
       </c>
@@ -4488,7 +4382,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>149</v>
       </c>
@@ -4529,7 +4423,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>151</v>
       </c>
@@ -4570,7 +4464,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>153</v>
       </c>
@@ -4611,7 +4505,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>157</v>
       </c>
@@ -4652,7 +4546,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>159</v>
       </c>
@@ -4693,7 +4587,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>161</v>
       </c>
@@ -4734,7 +4628,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>164</v>
       </c>
@@ -4775,7 +4669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>167</v>
       </c>
@@ -4816,7 +4710,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>169</v>
       </c>
@@ -4857,7 +4751,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>171</v>
       </c>
@@ -4898,7 +4792,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>174</v>
       </c>
@@ -4939,7 +4833,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>177</v>
       </c>
@@ -4980,7 +4874,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>179</v>
       </c>
@@ -5021,7 +4915,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>181</v>
       </c>
@@ -5062,7 +4956,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>183</v>
       </c>
@@ -5103,7 +4997,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>185</v>
       </c>
@@ -5144,7 +5038,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>188</v>
       </c>
@@ -5185,7 +5079,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>190</v>
       </c>
@@ -5226,7 +5120,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>192</v>
       </c>
@@ -5267,7 +5161,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>194</v>
       </c>
@@ -5308,7 +5202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>196</v>
       </c>
@@ -5349,7 +5243,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>199</v>
       </c>
@@ -5390,7 +5284,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>202</v>
       </c>
@@ -5431,7 +5325,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>204</v>
       </c>
@@ -5472,7 +5366,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>206</v>
       </c>
@@ -5513,7 +5407,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>208</v>
       </c>
@@ -5554,7 +5448,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>212</v>
       </c>
@@ -5595,7 +5489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>215</v>
       </c>
@@ -5636,7 +5530,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>218</v>
       </c>
@@ -5677,7 +5571,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>220</v>
       </c>
@@ -5718,7 +5612,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>222</v>
       </c>
@@ -5759,7 +5653,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>225</v>
       </c>
@@ -5800,7 +5694,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>227</v>
       </c>
@@ -5841,7 +5735,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>229</v>
       </c>
@@ -5882,7 +5776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>231</v>
       </c>
@@ -5923,7 +5817,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>233</v>
       </c>
@@ -5964,7 +5858,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>236</v>
       </c>
@@ -6005,7 +5899,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>238</v>
       </c>
@@ -6046,7 +5940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>240</v>
       </c>
@@ -6087,7 +5981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>242</v>
       </c>
@@ -6128,7 +6022,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>245</v>
       </c>
@@ -6169,7 +6063,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>247</v>
       </c>
@@ -6210,7 +6104,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>249</v>
       </c>
@@ -6251,7 +6145,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>251</v>
       </c>
@@ -6292,7 +6186,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>254</v>
       </c>
@@ -6333,7 +6227,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>258</v>
       </c>
@@ -6374,7 +6268,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>260</v>
       </c>
@@ -6415,7 +6309,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>262</v>
       </c>
@@ -6456,7 +6350,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>264</v>
       </c>
@@ -6497,7 +6391,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>266</v>
       </c>
@@ -6538,7 +6432,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>268</v>
       </c>
@@ -6579,7 +6473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>270</v>
       </c>
@@ -6620,7 +6514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>272</v>
       </c>
@@ -6661,7 +6555,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>274</v>
       </c>
@@ -6702,7 +6596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>278</v>
       </c>
@@ -6743,7 +6637,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>280</v>
       </c>
@@ -6784,7 +6678,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>282</v>
       </c>
@@ -6825,7 +6719,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>284</v>
       </c>
@@ -6866,7 +6760,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>290</v>
       </c>
@@ -6907,7 +6801,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>293</v>
       </c>
@@ -6948,7 +6842,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>296</v>
       </c>
@@ -6989,7 +6883,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>299</v>
       </c>
@@ -7030,7 +6924,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>302</v>
       </c>
@@ -7071,7 +6965,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>305</v>
       </c>
@@ -7112,7 +7006,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>307</v>
       </c>
@@ -7153,7 +7047,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>310</v>
       </c>
@@ -7194,7 +7088,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>316</v>
       </c>
@@ -7235,7 +7129,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>318</v>
       </c>
@@ -7276,7 +7170,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>320</v>
       </c>
@@ -7317,7 +7211,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>323</v>
       </c>
@@ -7358,7 +7252,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>325</v>
       </c>
@@ -7399,7 +7293,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>327</v>
       </c>
@@ -7440,7 +7334,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>331</v>
       </c>
@@ -7481,7 +7375,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>333</v>
       </c>
@@ -7522,7 +7416,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>335</v>
       </c>
@@ -7563,7 +7457,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>338</v>
       </c>
@@ -7604,7 +7498,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>341</v>
       </c>
@@ -7645,7 +7539,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>343</v>
       </c>
@@ -7686,7 +7580,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>345</v>
       </c>
@@ -7727,7 +7621,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>347</v>
       </c>
@@ -7768,7 +7662,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>350</v>
       </c>
@@ -7809,7 +7703,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>352</v>
       </c>
@@ -7850,7 +7744,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>354</v>
       </c>
@@ -7891,7 +7785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>357</v>
       </c>
@@ -7932,7 +7826,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>359</v>
       </c>
@@ -7973,7 +7867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>362</v>
       </c>
@@ -8014,7 +7908,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>364</v>
       </c>
@@ -8055,7 +7949,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>366</v>
       </c>
@@ -8096,7 +7990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>368</v>
       </c>
@@ -8137,7 +8031,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>370</v>
       </c>
@@ -8178,7 +8072,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>372</v>
       </c>
@@ -8219,7 +8113,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>377</v>
       </c>
@@ -8260,7 +8154,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>380</v>
       </c>
@@ -8301,7 +8195,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>383</v>
       </c>
@@ -8342,7 +8236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>386</v>
       </c>
@@ -8383,7 +8277,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>388</v>
       </c>
@@ -8424,7 +8318,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
         <v>391</v>
       </c>
@@ -8465,7 +8359,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>399</v>
       </c>
@@ -8506,7 +8400,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>401</v>
       </c>
@@ -8547,7 +8441,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>404</v>
       </c>
@@ -8588,7 +8482,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>407</v>
       </c>
@@ -8629,7 +8523,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>409</v>
       </c>
@@ -8670,7 +8564,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>412</v>
       </c>
@@ -8711,7 +8605,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>415</v>
       </c>
@@ -8752,7 +8646,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>417</v>
       </c>
@@ -8793,7 +8687,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>419</v>
       </c>
@@ -8834,7 +8728,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>421</v>
       </c>
@@ -8875,7 +8769,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>424</v>
       </c>
@@ -8916,7 +8810,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>426</v>
       </c>
@@ -8957,7 +8851,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>429</v>
       </c>
@@ -8998,7 +8892,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>432</v>
       </c>
@@ -9039,7 +8933,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>434</v>
       </c>
@@ -9080,7 +8974,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>437</v>
       </c>
@@ -9121,7 +9015,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>439</v>
       </c>
@@ -9162,7 +9056,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>441</v>
       </c>
@@ -9203,7 +9097,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>443</v>
       </c>
@@ -9244,7 +9138,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>445</v>
       </c>
@@ -9285,7 +9179,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>447</v>
       </c>
@@ -9326,7 +9220,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>449</v>
       </c>
@@ -9367,7 +9261,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>454</v>
       </c>
@@ -9408,7 +9302,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>456</v>
       </c>
@@ -9449,7 +9343,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>458</v>
       </c>
@@ -9490,7 +9384,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>461</v>
       </c>
@@ -9531,7 +9425,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>463</v>
       </c>
@@ -9572,7 +9466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>465</v>
       </c>
@@ -9613,7 +9507,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>467</v>
       </c>
@@ -9654,7 +9548,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>470</v>
       </c>
@@ -9695,7 +9589,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>473</v>
       </c>
@@ -9736,7 +9630,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>476</v>
       </c>
@@ -9777,7 +9671,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>478</v>
       </c>
@@ -9818,7 +9712,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>480</v>
       </c>
@@ -9859,7 +9753,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>483</v>
       </c>
@@ -9900,7 +9794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>485</v>
       </c>
@@ -9941,7 +9835,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>487</v>
       </c>
@@ -9982,7 +9876,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>490</v>
       </c>
@@ -10023,7 +9917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>492</v>
       </c>
@@ -10064,7 +9958,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>494</v>
       </c>
@@ -10105,7 +9999,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>497</v>
       </c>
@@ -10146,7 +10040,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>499</v>
       </c>
@@ -10187,7 +10081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>501</v>
       </c>
@@ -10228,7 +10122,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>504</v>
       </c>
@@ -10269,7 +10163,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>507</v>
       </c>
@@ -10310,7 +10204,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>509</v>
       </c>
@@ -10351,7 +10245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>512</v>
       </c>
@@ -10392,7 +10286,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>515</v>
       </c>
@@ -10433,7 +10327,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>517</v>
       </c>
@@ -10474,7 +10368,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>519</v>
       </c>
@@ -10515,7 +10409,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>522</v>
       </c>
@@ -10556,7 +10450,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>524</v>
       </c>
@@ -10597,7 +10491,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>526</v>
       </c>
@@ -10639,38 +10533,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M200"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:M200" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="2" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -10693,306 +10578,298 @@
         <v>534</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A2)</f>
+      <c r="C2" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A2)</f>
         <v>51</v>
       </c>
-      <c r="D2" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A2,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D2" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A2,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>26</v>
       </c>
-      <c r="E2" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A2,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E2" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A2,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>16</v>
       </c>
-      <c r="F2" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A2,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F2" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A2,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>9</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H2)</f>
+      <c r="I2" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H2)</f>
         <v>123</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A3)</f>
+      <c r="C3" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A3)</f>
         <v>55</v>
       </c>
-      <c r="D3" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A3,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D3" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A3,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>40</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A3,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E3" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A3,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>11</v>
       </c>
-      <c r="F3" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A3,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F3" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A3,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>4</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H3)</f>
+      <c r="I3" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H3)</f>
         <v>39</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>285</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A4)</f>
+      <c r="C4" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A4)</f>
         <v>8</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A4,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D4" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A4,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>7</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A4,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E4" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A4,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>1</v>
       </c>
-      <c r="F4" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A4,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F4" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A4,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>0</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H4)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I4" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H4)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>311</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A5)</f>
+      <c r="C5" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A5)</f>
         <v>25</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A5,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D5" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A5,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>25</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A5,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E5" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A5,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A5,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F5" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A5,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>0</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="I5" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H5)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$M$2:$M$200,$H5)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>373</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A6)</f>
+      <c r="C6" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A6)</f>
         <v>6</v>
       </c>
-      <c r="D6" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A6,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D6" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A6,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>5</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A6,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E6" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A6,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>1</v>
       </c>
-      <c r="F6" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A6,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F6" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A6,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>0</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="I6" s="11" t="n">
-        <f aca="false">SUM(I2:I5)</f>
+      <c r="I6" s="11">
+        <f>SUM(I2:I5)</f>
         <v>199</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>536</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A7)</f>
+      <c r="C7" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A7,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D7" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A7,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A7,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E7" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A7,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>0</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A7,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F7" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A7,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>537</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A8)</f>
+      <c r="C8" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A8,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D8" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A8,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A8,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E8" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A8,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>0</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A8,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F8" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A8,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>392</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A9)</f>
-        <v>22</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A9,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
-        <v>20</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A9,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="C9" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A9)</f>
+        <v>22</v>
+      </c>
+      <c r="D9" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A9,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+        <v>20</v>
+      </c>
+      <c r="E9" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A9,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>2</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A9,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F9" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A9,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>450</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <f aca="false">COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A10)</f>
+      <c r="C10" s="10">
+        <f>COUNTIF('Matriz de Trazabilidad'!$B$2:$B$200,$A10)</f>
         <v>32</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A10,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
+      <c r="D10" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A10,'Matriz de Trazabilidad'!$I$2:$I$200,"Alta")</f>
         <v>18</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A10,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
+      <c r="E10" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A10,'Matriz de Trazabilidad'!$I$2:$I$200,"Moderada")</f>
         <v>12</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <f aca="false">COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A10,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
+      <c r="F10" s="10">
+        <f>COUNTIFS('Matriz de Trazabilidad'!$B$2:$B$200,$A10,'Matriz de Trazabilidad'!$I$2:$I$200,"Baja")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <f aca="false">SUM(C2:C10)</f>
+      <c r="C11" s="11">
+        <f>SUM(C2:C10)</f>
         <v>199</v>
       </c>
-      <c r="D11" s="11" t="n">
-        <f aca="false">SUM(D2:D10)</f>
+      <c r="D11" s="11">
+        <f>SUM(D2:D10)</f>
         <v>141</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <f aca="false">SUM(E2:E10)</f>
+      <c r="E11" s="11">
+        <f>SUM(E2:E10)</f>
         <v>43</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <f aca="false">SUM(F2:F10)</f>
+      <c r="F11" s="11">
+        <f>SUM(F2:F10)</f>
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>538</v>
       </c>
@@ -11012,7 +10889,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>542</v>
       </c>
@@ -11025,14 +10902,14 @@
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>545</v>
       </c>
@@ -11045,14 +10922,14 @@
       <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="2">
         <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" ht="280.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>548</v>
       </c>
@@ -11065,14 +10942,14 @@
       <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="2">
         <v>148</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>551</v>
       </c>
@@ -11085,14 +10962,14 @@
       <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="2">
         <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>554</v>
       </c>
@@ -11105,14 +10982,14 @@
       <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>556</v>
       </c>
@@ -11125,14 +11002,14 @@
       <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="2">
         <v>7</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>559</v>
       </c>
@@ -11145,14 +11022,14 @@
       <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="2">
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>561</v>
       </c>
@@ -11165,14 +11042,14 @@
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="2">
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>564</v>
       </c>
@@ -11185,14 +11062,14 @@
       <c r="D10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="2">
         <v>23</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>567</v>
       </c>
@@ -11205,14 +11082,14 @@
       <c r="D11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="2">
         <v>3</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:6" ht="293.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>570</v>
       </c>
@@ -11225,14 +11102,14 @@
       <c r="D12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="2">
         <v>159</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:6" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>573</v>
       </c>
@@ -11245,14 +11122,14 @@
       <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="2">
         <v>43</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:6" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>292</v>
       </c>
@@ -11265,14 +11142,14 @@
       <c r="D14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="2">
         <v>94</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>578</v>
       </c>
@@ -11285,14 +11162,14 @@
       <c r="D15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="2">
         <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:6" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>581</v>
       </c>
@@ -11305,14 +11182,14 @@
       <c r="D16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="2">
         <v>95</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>584</v>
       </c>
@@ -11325,14 +11202,14 @@
       <c r="D17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="2">
         <v>1</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>586</v>
       </c>
@@ -11345,14 +11222,14 @@
       <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="2">
         <v>1</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>588</v>
       </c>
@@ -11365,14 +11242,14 @@
       <c r="D19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>591</v>
       </c>
@@ -11385,14 +11262,14 @@
       <c r="D20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>594</v>
       </c>
@@ -11405,14 +11282,14 @@
       <c r="D21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="2">
         <v>1</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>596</v>
       </c>
@@ -11425,14 +11302,14 @@
       <c r="D22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="2">
         <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>599</v>
       </c>
@@ -11445,14 +11322,14 @@
       <c r="D23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="2">
         <v>1</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>601</v>
       </c>
@@ -11465,14 +11342,14 @@
       <c r="D24" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="12">
         <v>0</v>
       </c>
       <c r="F24" s="13" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>604</v>
       </c>
@@ -11485,14 +11362,14 @@
       <c r="D25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="2">
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>607</v>
       </c>
@@ -11505,14 +11382,14 @@
       <c r="D26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="2">
         <v>2</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>610</v>
       </c>
@@ -11525,14 +11402,14 @@
       <c r="D27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="4">
         <v>0</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>613</v>
       </c>
@@ -11545,14 +11422,14 @@
       <c r="D28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="2">
         <v>1</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>298</v>
       </c>
@@ -11565,14 +11442,14 @@
       <c r="D29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="2">
         <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>617</v>
       </c>
@@ -11585,7 +11462,7 @@
       <c r="D30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="2">
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -11593,14 +11470,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F30"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:F30" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>